--- a/Audit/JJ_PD_IP_D27_통합테스트계획서_v1.0_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_D27_통합테스트계획서_v1.0_이노팸.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-10940" yWindow="-28200" windowWidth="30240" windowHeight="27280" tabRatio="742" firstSheet="4" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4320" yWindow="1120" windowWidth="41820" windowHeight="22460" tabRatio="742" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표지" sheetId="1" state="visible" r:id="rId1"/>
@@ -67,18 +67,182 @@
     <definedName name="\O">'[3]9GNG운반'!#REF!</definedName>
     <definedName name="\P">'[3]9GNG운반'!#REF!</definedName>
     <definedName name="\Q">'[3]9GNG운반'!#REF!</definedName>
+    <definedName name="ㄱ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㄱㄱㄷㄱ">#REF!</definedName>
+    <definedName name="ㄱㅎㄷㄱㅎ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="개정이력">[5]단계별측정!#REF!</definedName>
+    <definedName name="결과조건">'[4]Defect 코드'!#REF!</definedName>
+    <definedName name="결함유형">'[4]Defect 코드'!#REF!</definedName>
+    <definedName name="계획표">#REF!</definedName>
+    <definedName name="공사설명서" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="과업">[11]COST!#REF!</definedName>
+    <definedName name="과업대비표1">#REF!</definedName>
+    <definedName name="관련근거구분">[12]검증자료!$A$2:$A$6</definedName>
+    <definedName name="국소수_서울">#REF!</definedName>
+    <definedName name="기존프로그램">#REF!</definedName>
+    <definedName name="기준용어">#REF!</definedName>
+    <definedName name="ㄴ" hidden="1">#REF!</definedName>
+    <definedName name="ㄴㄴ">[13]단계별측정!#REF!</definedName>
+    <definedName name="ㄴㄴㄱ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴ아러" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="나" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="납기1">[10]IN!$B$5</definedName>
+    <definedName name="납기2">[14]IN!$B$5</definedName>
+    <definedName name="납기3">[10]IN!$D$5</definedName>
+    <definedName name="납기4">[14]IN!$D$5</definedName>
+    <definedName name="ㄷ가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄷㄷㄷ">#REF!</definedName>
+    <definedName name="다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="단가">#REF!</definedName>
+    <definedName name="데이터그룹">'[15]데이터그룹(참고)'!#REF!</definedName>
+    <definedName name="데이터그룹명칭">[16]DI_데이터그룹!#REF!</definedName>
+    <definedName name="도">#REF!</definedName>
+    <definedName name="두지" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="둑ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄹㅇㅁㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="라" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅁ" hidden="1">#REF!</definedName>
+    <definedName name="ㅁㅁㅁ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="마" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="문서명">"단위시험 결과서"</definedName>
+    <definedName name="문서번호표시">"Document #: " &amp; DocumentName</definedName>
+    <definedName name="ㅁㄻㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅂ" hidden="1">#REF!</definedName>
+    <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="바" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="버전">"Version " &amp; Version</definedName>
+    <definedName name="변경내역" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="보" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="분류">#REF!</definedName>
+    <definedName name="ㅅㅅㅅ" hidden="1">#REF!</definedName>
+    <definedName name="사" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="사용빈도">#N/A</definedName>
+    <definedName name="속성유형">[17]코드!$D$2:$D$3</definedName>
+    <definedName name="수" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수용여부">[12]검증자료!$C$2:$C$3</definedName>
+    <definedName name="수정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정5" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정6" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="시스템가능성">#REF!</definedName>
+    <definedName name="시스템명">"IVR시스템 연계 및 개발"</definedName>
+    <definedName name="시스템분류">[18]공통코드!#REF!</definedName>
+    <definedName name="시스템유형명">[18]공통코드!$A$10:$A$15</definedName>
+    <definedName name="시스템코드">[18]공통코드!#REF!</definedName>
+    <definedName name="시스템화가능성">#N/A</definedName>
+    <definedName name="신설변경" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="심각도">'[4]Defect 코드'!#REF!</definedName>
+    <definedName name="ㅇ45">#REF!</definedName>
+    <definedName name="ㅇ나닐ㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㄹㅇ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㄹㅈㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㅇㄹㅈㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇ아" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㅀㅇㅁㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="아" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ지" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅗㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="알람관리">#REF!</definedName>
+    <definedName name="업무대기능">'[19]업무대기능(참고)'!$A$2:$A$14</definedName>
+    <definedName name="업무중요도">[20]공통코드!#REF!</definedName>
+    <definedName name="위치">[18]공통코드!$F$2:$F$9</definedName>
+    <definedName name="유형구분">[12]검증자료!$B$2:$B$3</definedName>
+    <definedName name="응용기능관계">#REF!</definedName>
+    <definedName name="응용기능관계명칭">#REF!</definedName>
+    <definedName name="응용시스템상태">#REF!</definedName>
+    <definedName name="응용시스템상태_코드">#REF!</definedName>
+    <definedName name="응용시스템상태선택">[18]공통코드!$A$2:$A$7</definedName>
+    <definedName name="응용시스템상태코드">#REF!</definedName>
+    <definedName name="응용시스템코드">[18]공통코드!#REF!</definedName>
+    <definedName name="이력">[5]검토측정!#REF!</definedName>
+    <definedName name="이름" hidden="1">#REF!</definedName>
+    <definedName name="이름1">#REF!</definedName>
+    <definedName name="일반현황__2_">#REF!</definedName>
+    <definedName name="일반현황_3">#REF!</definedName>
+    <definedName name="일일대가1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈㅂㄷㅈㅂㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자ㅓㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="재료집계3">#REF!</definedName>
+    <definedName name="저장소">#REF!</definedName>
+    <definedName name="저장소구분">#REF!</definedName>
+    <definedName name="저장소구분1">#REF!</definedName>
+    <definedName name="전기출력2">[21]ELEC!$B$3:$M$3,[21]ELEC!$B$4:$M$4,[21]ELEC!$B$5:$M$5,[21]ELEC!$B$7:$M$7</definedName>
+    <definedName name="전기출력3">[21]ELEC!$B$3:$M$3,[21]ELEC!$B$6:$M$6,[21]ELEC!$B$8:$M$8</definedName>
+    <definedName name="정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="제주추가종합수정안" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="주사용자">[22]공통코드!$D$2:$D$4</definedName>
+    <definedName name="중계기현황">#REF!</definedName>
+    <definedName name="지더" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="지두" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="직종">#REF!</definedName>
+    <definedName name="차" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="총괄11" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="충남신설">#REF!</definedName>
+    <definedName name="충북신설">#REF!</definedName>
+    <definedName name="ㅋ">#REF!</definedName>
+    <definedName name="ㅋㅋ">[13]단계별측정!#REF!</definedName>
+    <definedName name="ㅋㅋㅋ">#REF!</definedName>
+    <definedName name="카" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="콤보_데이터그룹">'[4]데이터그룹(참고)'!#REF!</definedName>
+    <definedName name="타" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="특별시방서1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="파" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="평가결과">'[4]Defect 코드'!#REF!</definedName>
+    <definedName name="표준용어">#REF!</definedName>
+    <definedName name="표준프로세스">#REF!</definedName>
+    <definedName name="프로젝트명">"민원시스템 백업장비 도입 및 노후장비 교체"</definedName>
+    <definedName name="하" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="한" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="합계">#REF!</definedName>
+    <definedName name="협업포탈_1">'[2]예정(3)'!#REF!</definedName>
+    <definedName name="홎ㅅㄱ도" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ도">#REF!</definedName>
+    <definedName name="ㅏ딪" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ아">#REF!</definedName>
+    <definedName name="ㅏ잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ짇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄴ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅓ아ㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅗㄷ">#REF!</definedName>
+    <definedName name="ㅗㅎㄷ">#REF!</definedName>
+    <definedName name="ㅜ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ자ㅣㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅠ">#REF!</definedName>
+    <definedName name="ㅠㄹㅇ">#REF!</definedName>
+    <definedName name="ㅣ닺" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ잗" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ젇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄻㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="A">#REF!</definedName>
     <definedName name="A000">#REF!</definedName>
     <definedName name="a2121212">'[3]9GNG운반'!#REF!</definedName>
     <definedName name="AA" hidden="1">#REF!</definedName>
     <definedName name="AAA">#REF!</definedName>
-    <definedName name="aaaa">'[5]응용시스템(참고)'!#REF!</definedName>
+    <definedName name="aaaa">'[4]응용시스템(참고)'!#REF!</definedName>
     <definedName name="AAAAA">#REF!</definedName>
     <definedName name="add">#REF!</definedName>
     <definedName name="ARSCC">#REF!</definedName>
     <definedName name="ASIC">#REF!</definedName>
-    <definedName name="b">[4]단계별측정!#REF!</definedName>
-    <definedName name="baseline">'[5]2.일정추적'!#REF!</definedName>
+    <definedName name="b">[5]단계별측정!#REF!</definedName>
+    <definedName name="baseline">'[4]2.일정추적'!#REF!</definedName>
     <definedName name="bb">'[3]9GNG운반'!#REF!</definedName>
     <definedName name="BTSINFO_991Q">#REF!</definedName>
     <definedName name="BTSINFO_992Q">#REF!</definedName>
@@ -97,8 +261,8 @@
     <definedName name="CHC_경기">#REF!</definedName>
     <definedName name="CHC_서울">#REF!</definedName>
     <definedName name="CHC_서울_COUNT">#REF!</definedName>
-    <definedName name="CHC산출_경기">'[19]Calc V1.2'!$H$1:$AC$65536</definedName>
-    <definedName name="CHC산출_서울">'[19]Calc V1.2 (2)'!$H$1:$AC$65536</definedName>
+    <definedName name="CHC산출_경기">'[6]Calc V1.2'!$H$1:$AC$65536</definedName>
+    <definedName name="CHC산출_서울">'[6]Calc V1.2 (2)'!$H$1:$AC$65536</definedName>
     <definedName name="Comments">#REF!</definedName>
     <definedName name="cost_a">#REF!</definedName>
     <definedName name="cost_b">#REF!</definedName>
@@ -116,9 +280,9 @@
     <definedName name="DocumentName">"OE-TS-UTR-001"</definedName>
     <definedName name="dsfga" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="DTIC">#REF!</definedName>
-    <definedName name="e">[4]단계별측정!#REF!</definedName>
-    <definedName name="ee">[4]단계별측정!#REF!</definedName>
-    <definedName name="eeeeee">[4]단계별측정!#REF!</definedName>
+    <definedName name="e">[5]단계별측정!#REF!</definedName>
+    <definedName name="ee">[5]단계별측정!#REF!</definedName>
+    <definedName name="eeeeee">[5]단계별측정!#REF!</definedName>
     <definedName name="effort_a">#REF!</definedName>
     <definedName name="effort_change">#REF!</definedName>
     <definedName name="effort_e">#REF!</definedName>
@@ -129,16 +293,16 @@
     <definedName name="EI_first_row">#REF!</definedName>
     <definedName name="EI_Name">#REF!</definedName>
     <definedName name="EI_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 50)), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
+    <definedName name="ENG_개체전">#REF!</definedName>
+    <definedName name="ENG_개체후">#REF!</definedName>
     <definedName name="ENG_Data">#REF!</definedName>
     <definedName name="ENG_Data_서울">#REF!</definedName>
     <definedName name="ENG_Data_증설후">#REF!</definedName>
-    <definedName name="ENG_개체전">#REF!</definedName>
-    <definedName name="ENG_개체후">#REF!</definedName>
     <definedName name="ENG11차">#REF!</definedName>
     <definedName name="ENGDATA">#REF!</definedName>
     <definedName name="Entity_List">#REF!</definedName>
     <definedName name="er" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="Est_Eff_MDay">[20]FPA!#REF!</definedName>
+    <definedName name="Est_Eff_MDay">[7]FPA!#REF!</definedName>
     <definedName name="ex_rate">#REF!</definedName>
     <definedName name="FA_서울">#REF!</definedName>
     <definedName name="fdssdsdfds">#REF!</definedName>
@@ -155,12 +319,12 @@
     <definedName name="hejlkw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="hsdgfjhf" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ICPC">#REF!</definedName>
-    <definedName name="Index">'[21]Data Vol'!$B$6:$E$6816</definedName>
+    <definedName name="Index">'[8]Data Vol'!$B$6:$E$6816</definedName>
     <definedName name="IT_A">IF( OR(AND(#REF!&lt;2,#REF!&gt;15), AND(#REF!=2, AND(#REF!&gt;= 5,#REF!&lt;= 15)), AND(#REF!&gt;2, AND(#REF!&gt;=1,#REF!&lt;= 4)) ),1,0)</definedName>
     <definedName name="IT_C">IF( OR(AND(#REF!=2,#REF!&gt; 15), AND(#REF!&gt;2,#REF!&gt;=  5) ),1,0)</definedName>
     <definedName name="IT_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 15)), AND(#REF!=2, AND(#REF!&gt;= 1,#REF!&lt;= 4)) ),1,0)</definedName>
-    <definedName name="itsa_ratio_nrec">[22]공수견적!#REF!</definedName>
-    <definedName name="itsa_ratio_rec">[20]순수개발!#REF!</definedName>
+    <definedName name="itsa_ratio_nrec">[9]공수견적!#REF!</definedName>
+    <definedName name="itsa_ratio_rec">[7]순수개발!#REF!</definedName>
     <definedName name="IWFIC" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jdkl" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jeklw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -182,8 +346,8 @@
     <definedName name="MSIC">#REF!</definedName>
     <definedName name="MSICC">#REF!</definedName>
     <definedName name="MTC">#REF!</definedName>
-    <definedName name="name">[9]IN!$D$5</definedName>
-    <definedName name="name1">[9]IN!$D$5</definedName>
+    <definedName name="name">[10]IN!$D$5</definedName>
+    <definedName name="name1">[10]IN!$D$5</definedName>
     <definedName name="NESC">#REF!</definedName>
     <definedName name="NO">#REF!</definedName>
     <definedName name="OCPC">#REF!</definedName>
@@ -208,7 +372,7 @@
     <definedName name="review_defect">#REF!</definedName>
     <definedName name="review_error">#REF!</definedName>
     <definedName name="RMS">#REF!</definedName>
-    <definedName name="rpt_date">'[5]1.요약'!$C$4</definedName>
+    <definedName name="rpt_date">'[4]1.요약'!$C$4</definedName>
     <definedName name="rr" hidden="1">#REF!</definedName>
     <definedName name="RRR" hidden="1">#REF!</definedName>
     <definedName name="s" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
@@ -219,7 +383,7 @@
     <definedName name="schedule_e_s">#REF!</definedName>
     <definedName name="SEC_서울">#REF!</definedName>
     <definedName name="Severity">#REF!</definedName>
-    <definedName name="size_code_e">[4]소스코드크기측정!#REF!</definedName>
+    <definedName name="size_code_e">[5]소스코드크기측정!#REF!</definedName>
     <definedName name="SS" hidden="1">#REF!</definedName>
     <definedName name="SSD">#REF!</definedName>
     <definedName name="SSN7C">#REF!</definedName>
@@ -227,8 +391,8 @@
     <definedName name="staffMonth">#REF!</definedName>
     <definedName name="staffWeek">#REF!</definedName>
     <definedName name="State_of_Origin">#REF!</definedName>
-    <definedName name="Status">'[5]Defect 코드'!#REF!</definedName>
-    <definedName name="tol">'[5]4.1공수분석_개발'!$J$6</definedName>
+    <definedName name="Status">'[4]Defect 코드'!#REF!</definedName>
+    <definedName name="tol">'[4]4.1공수분석_개발'!$J$6</definedName>
     <definedName name="TOTAL" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="tt" hidden="1">#REF!</definedName>
     <definedName name="TTT">#REF!</definedName>
@@ -277,170 +441,6 @@
     <definedName name="wte" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ww" hidden="1">#REF!</definedName>
     <definedName name="zzzzzzzzzzzzzzzzzzz">#REF!</definedName>
-    <definedName name="ㄱ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㄱㄱㄷㄱ">#REF!</definedName>
-    <definedName name="ㄱㅎㄷㄱㅎ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="개정이력">[4]단계별측정!#REF!</definedName>
-    <definedName name="결과조건">'[5]Defect 코드'!#REF!</definedName>
-    <definedName name="결함유형">'[5]Defect 코드'!#REF!</definedName>
-    <definedName name="계획표">#REF!</definedName>
-    <definedName name="공사설명서" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업">[6]COST!#REF!</definedName>
-    <definedName name="과업대비표1">#REF!</definedName>
-    <definedName name="관련근거구분">[7]검증자료!$A$2:$A$6</definedName>
-    <definedName name="국소수_서울">#REF!</definedName>
-    <definedName name="기존프로그램">#REF!</definedName>
-    <definedName name="기준용어">#REF!</definedName>
-    <definedName name="ㄴ" hidden="1">#REF!</definedName>
-    <definedName name="ㄴㄴ">[8]단계별측정!#REF!</definedName>
-    <definedName name="ㄴㄴㄱ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴ아러" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="나" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="납기1">[9]IN!$B$5</definedName>
-    <definedName name="납기2">[10]IN!$B$5</definedName>
-    <definedName name="납기3">[9]IN!$D$5</definedName>
-    <definedName name="납기4">[10]IN!$D$5</definedName>
-    <definedName name="ㄷ가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄷㄷㄷ">#REF!</definedName>
-    <definedName name="다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="단가">#REF!</definedName>
-    <definedName name="데이터그룹">'[11]데이터그룹(참고)'!#REF!</definedName>
-    <definedName name="데이터그룹명칭">[12]DI_데이터그룹!#REF!</definedName>
-    <definedName name="도">#REF!</definedName>
-    <definedName name="두지" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="둑ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄹㅇㅁㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="라" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄻㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁ" hidden="1">#REF!</definedName>
-    <definedName name="ㅁㄻㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㅁㅁ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="마" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="문서명">"단위시험 결과서"</definedName>
-    <definedName name="문서번호표시">"Document #: " &amp; DocumentName</definedName>
-    <definedName name="ㅂ" hidden="1">#REF!</definedName>
-    <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="바" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="버전">"Version " &amp; Version</definedName>
-    <definedName name="변경내역" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="보" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="분류">#REF!</definedName>
-    <definedName name="ㅅㅅㅅ" hidden="1">#REF!</definedName>
-    <definedName name="사" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="사용빈도">#N/A</definedName>
-    <definedName name="속성유형">[13]코드!$D$2:$D$3</definedName>
-    <definedName name="수" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수용여부">[7]검증자료!$C$2:$C$3</definedName>
-    <definedName name="수정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정5" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정6" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="시스템가능성">#REF!</definedName>
-    <definedName name="시스템명">"IVR시스템 연계 및 개발"</definedName>
-    <definedName name="시스템분류">[14]공통코드!#REF!</definedName>
-    <definedName name="시스템유형명">[14]공통코드!$A$10:$A$15</definedName>
-    <definedName name="시스템코드">[14]공통코드!#REF!</definedName>
-    <definedName name="시스템화가능성">#N/A</definedName>
-    <definedName name="신설변경" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="심각도">'[5]Defect 코드'!#REF!</definedName>
-    <definedName name="ㅇ45">#REF!</definedName>
-    <definedName name="ㅇ나닐ㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㄹㅇ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㄹㅈㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㅀㅇㅁㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㅇㄹㅈㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇ아" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="아" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ지" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅗㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="알람관리">#REF!</definedName>
-    <definedName name="업무대기능">'[15]업무대기능(참고)'!$A$2:$A$14</definedName>
-    <definedName name="업무중요도">[16]공통코드!#REF!</definedName>
-    <definedName name="위치">[14]공통코드!$F$2:$F$9</definedName>
-    <definedName name="유형구분">[7]검증자료!$B$2:$B$3</definedName>
-    <definedName name="응용기능관계">#REF!</definedName>
-    <definedName name="응용기능관계명칭">#REF!</definedName>
-    <definedName name="응용시스템상태">#REF!</definedName>
-    <definedName name="응용시스템상태_코드">#REF!</definedName>
-    <definedName name="응용시스템상태선택">[14]공통코드!$A$2:$A$7</definedName>
-    <definedName name="응용시스템상태코드">#REF!</definedName>
-    <definedName name="응용시스템코드">[14]공통코드!#REF!</definedName>
-    <definedName name="이력">[4]검토측정!#REF!</definedName>
-    <definedName name="이름" hidden="1">#REF!</definedName>
-    <definedName name="이름1">#REF!</definedName>
-    <definedName name="일반현황__2_">#REF!</definedName>
-    <definedName name="일반현황_3">#REF!</definedName>
-    <definedName name="일일대가1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈㅂㄷㅈㅂㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자ㅓㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="재료집계3">#REF!</definedName>
-    <definedName name="저장소">#REF!</definedName>
-    <definedName name="저장소구분">#REF!</definedName>
-    <definedName name="저장소구분1">#REF!</definedName>
-    <definedName name="전기출력2">[17]ELEC!$B$3:$M$3,[17]ELEC!$B$4:$M$4,[17]ELEC!$B$5:$M$5,[17]ELEC!$B$7:$M$7</definedName>
-    <definedName name="전기출력3">[17]ELEC!$B$3:$M$3,[17]ELEC!$B$6:$M$6,[17]ELEC!$B$8:$M$8</definedName>
-    <definedName name="정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="제주추가종합수정안" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="주사용자">[18]공통코드!$D$2:$D$4</definedName>
-    <definedName name="중계기현황">#REF!</definedName>
-    <definedName name="지더" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="지두" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="직종">#REF!</definedName>
-    <definedName name="차" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="총괄11" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="충남신설">#REF!</definedName>
-    <definedName name="충북신설">#REF!</definedName>
-    <definedName name="ㅋ">#REF!</definedName>
-    <definedName name="ㅋㅋ">[8]단계별측정!#REF!</definedName>
-    <definedName name="ㅋㅋㅋ">#REF!</definedName>
-    <definedName name="카" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="콤보_데이터그룹">'[5]데이터그룹(참고)'!#REF!</definedName>
-    <definedName name="타" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="특별시방서1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="파" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="평가결과">'[5]Defect 코드'!#REF!</definedName>
-    <definedName name="표준용어">#REF!</definedName>
-    <definedName name="표준프로세스">#REF!</definedName>
-    <definedName name="프로젝트명">"민원시스템 백업장비 도입 및 노후장비 교체"</definedName>
-    <definedName name="하" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="한" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="합계">#REF!</definedName>
-    <definedName name="협업포탈_1">'[2]예정(3)'!#REF!</definedName>
-    <definedName name="홎ㅅㄱ도" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ도">#REF!</definedName>
-    <definedName name="ㅏ딪" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ아">#REF!</definedName>
-    <definedName name="ㅏ잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ짇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄴ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅓ아ㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅗㄷ">#REF!</definedName>
-    <definedName name="ㅗㅎㄷ">#REF!</definedName>
-    <definedName name="ㅜ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ자ㅣㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅠ">#REF!</definedName>
-    <definedName name="ㅠㄹㅇ">#REF!</definedName>
-    <definedName name="ㅣ닺" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ잗" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ젇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="_" localSheetId="0">#REF!</definedName>
     <definedName name="__" localSheetId="0">#REF!</definedName>
     <definedName name="_80486SX_25" localSheetId="0">[23]COST!#REF!</definedName>
@@ -457,13 +457,110 @@
     <definedName name="\O" localSheetId="0">'[24]9GNG운반'!#REF!</definedName>
     <definedName name="\P" localSheetId="0">'[24]9GNG운반'!#REF!</definedName>
     <definedName name="\Q" localSheetId="0">'[24]9GNG운반'!#REF!</definedName>
+    <definedName name="ㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="계획표" localSheetId="0">#REF!</definedName>
+    <definedName name="공사설명서" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="과업" localSheetId="0">[23]COST!#REF!</definedName>
+    <definedName name="과업대비표1" localSheetId="0">#REF!</definedName>
+    <definedName name="국소수_서울" localSheetId="0">#REF!</definedName>
+    <definedName name="기존프로그램" localSheetId="0">#REF!</definedName>
+    <definedName name="ㄴㄴ" localSheetId="0">[32]단계별측정!#REF!</definedName>
+    <definedName name="ㄴㄴㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴ아러" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="나" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="납기1" localSheetId="0">[30]IN!$B$5</definedName>
+    <definedName name="납기2" localSheetId="0">[33]IN!$B$5</definedName>
+    <definedName name="납기3" localSheetId="0">[30]IN!$D$5</definedName>
+    <definedName name="납기4" localSheetId="0">[33]IN!$D$5</definedName>
+    <definedName name="ㄷ가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="두지" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="둑ㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄹㅇㅁㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="라" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅁㅁㅁ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="마" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="문서번호표시" localSheetId="0">"Document #: " &amp; DocumentName</definedName>
+    <definedName name="ㅁㄻㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅂㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="바" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="버전" localSheetId="0">"Version " &amp; Version</definedName>
+    <definedName name="변경내역" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="보" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="사" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정2" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정3" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정4" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정5" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정6" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="신설변경" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇ나닐ㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㄹㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㄹㅈㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㅇㄹㅈㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇ아" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㅀㅇㅁㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="아" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ지" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅗㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="이름" localSheetId="0" hidden="1">#REF!</definedName>
+    <definedName name="이름1" localSheetId="0">#REF!</definedName>
+    <definedName name="일반현황__2_" localSheetId="0">#REF!</definedName>
+    <definedName name="일일대가1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="잊" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈㅂㄷㅈㅂㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자ㅓㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="정" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="제주추가종합수정안" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="지더" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="지두" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="차" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="총괄11" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅋㅋ" localSheetId="0">[32]단계별측정!#REF!</definedName>
+    <definedName name="ㅋㅋㅋ" localSheetId="0">#REF!</definedName>
+    <definedName name="카" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="타" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="특별시방서1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="파" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="하" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="한" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="홎ㅅㄱ도" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ딪" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ잊" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ짇" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄴ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅓ아ㅣㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜㅈ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ자ㅣㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ닺" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅈ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ잗" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ젇" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄻㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="A" localSheetId="0">#REF!</definedName>
     <definedName name="A000" localSheetId="0">#REF!</definedName>
     <definedName name="a2121212" localSheetId="0">'[24]9GNG운반'!#REF!</definedName>
     <definedName name="AA" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="AAA" localSheetId="0">#REF!</definedName>
     <definedName name="AAAA" localSheetId="0">#REF!</definedName>
-    <definedName name="baseline" localSheetId="0">[28]CSR납기분석!#REF!</definedName>
+    <definedName name="baseline" localSheetId="0">[25]CSR납기분석!#REF!</definedName>
     <definedName name="bb" localSheetId="0">'[24]9GNG운반'!#REF!</definedName>
     <definedName name="BTSINFO_991Q" localSheetId="0">#REF!</definedName>
     <definedName name="BTSINFO_992Q" localSheetId="0">#REF!</definedName>
@@ -477,8 +574,8 @@
     <definedName name="CAMPC" localSheetId="0">#REF!</definedName>
     <definedName name="cause" localSheetId="0">#REF!</definedName>
     <definedName name="CB_1" localSheetId="0">#REF!</definedName>
-    <definedName name="CHC산출_경기" localSheetId="0">'[29]Calc V1.2'!$H$1:$AC$65536</definedName>
-    <definedName name="CHC산출_서울" localSheetId="0">'[29]Calc V1.2 (2)'!$H$1:$AC$65536</definedName>
+    <definedName name="CHC산출_경기" localSheetId="0">'[26]Calc V1.2'!$H$1:$AC$65536</definedName>
+    <definedName name="CHC산출_서울" localSheetId="0">'[26]Calc V1.2 (2)'!$H$1:$AC$65536</definedName>
     <definedName name="Comments" localSheetId="0">#REF!</definedName>
     <definedName name="cost_a" localSheetId="0">#REF!</definedName>
     <definedName name="cost_b" localSheetId="0">#REF!</definedName>
@@ -497,7 +594,7 @@
     <definedName name="EI_C" localSheetId="0">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=5),#REF!&gt; 50), AND(#REF!&gt;5,#REF!&gt;=  20) ),1,0)</definedName>
     <definedName name="EI_S" localSheetId="0">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 50)), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
     <definedName name="er" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="Est_Eff_MDay" localSheetId="0">[30]FPA!#REF!</definedName>
+    <definedName name="Est_Eff_MDay" localSheetId="0">[27]FPA!#REF!</definedName>
     <definedName name="ex_rate" localSheetId="0">#REF!</definedName>
     <definedName name="FA_서울" localSheetId="0">#REF!</definedName>
     <definedName name="fdssdsdfds" localSheetId="0">#REF!</definedName>
@@ -510,12 +607,12 @@
     <definedName name="H" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="hejlkw" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="hsdgfjhf" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="Index" localSheetId="0">'[31]Data Vol'!$B$6:$E$6816</definedName>
+    <definedName name="Index" localSheetId="0">'[28]Data Vol'!$B$6:$E$6816</definedName>
     <definedName name="IT_A" localSheetId="0">IF( OR(AND(#REF!&lt;2,#REF!&gt;15), AND(#REF!=2, AND(#REF!&gt;= 5,#REF!&lt;= 15)), AND(#REF!&gt;2, AND(#REF!&gt;=1,#REF!&lt;= 4)) ),1,0)</definedName>
     <definedName name="IT_C" localSheetId="0">IF( OR(AND(#REF!=2,#REF!&gt; 15), AND(#REF!&gt;2,#REF!&gt;=  5) ),1,0)</definedName>
     <definedName name="IT_S" localSheetId="0">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 15)), AND(#REF!=2, AND(#REF!&gt;= 1,#REF!&lt;= 4)) ),1,0)</definedName>
-    <definedName name="itsa_ratio_nrec" localSheetId="0">[32]공수견적!#REF!</definedName>
-    <definedName name="itsa_ratio_rec" localSheetId="0">[30]순수개발!#REF!</definedName>
+    <definedName name="itsa_ratio_nrec" localSheetId="0">[29]공수견적!#REF!</definedName>
+    <definedName name="itsa_ratio_rec" localSheetId="0">[27]순수개발!#REF!</definedName>
     <definedName name="IWFIC" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jdkl" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jeklw" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -531,8 +628,8 @@
     <definedName name="LastRow" localSheetId="0">#REF!</definedName>
     <definedName name="LPA_서울" localSheetId="0">#REF!</definedName>
     <definedName name="LRIC" localSheetId="0">#REF!</definedName>
-    <definedName name="name" localSheetId="0">[26]IN!$D$5</definedName>
-    <definedName name="name1" localSheetId="0">[26]IN!$D$5</definedName>
+    <definedName name="name" localSheetId="0">[30]IN!$D$5</definedName>
+    <definedName name="name1" localSheetId="0">[30]IN!$D$5</definedName>
     <definedName name="NESC" localSheetId="0">#REF!</definedName>
     <definedName name="NO" localSheetId="0">#REF!</definedName>
     <definedName name="OCPC" localSheetId="0">#REF!</definedName>
@@ -549,14 +646,14 @@
     <definedName name="QT_C" localSheetId="0">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=3),#REF!&gt; 19), AND(#REF!&gt;3,#REF!&gt;=  6) ),1,0)</definedName>
     <definedName name="QT_S" localSheetId="0">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 19)), AND(AND(#REF!&gt;=2,#REF!&lt;=3), AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
     <definedName name="RC0_서울" localSheetId="0">#REF!</definedName>
-    <definedName name="rpt_date" localSheetId="0">[33]요약!$C$4</definedName>
+    <definedName name="rpt_date" localSheetId="0">[31]요약!$C$4</definedName>
     <definedName name="rr" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="RRR" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="s" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="SS" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="SSD" localSheetId="0">#REF!</definedName>
     <definedName name="SSN7C" localSheetId="0">#REF!</definedName>
-    <definedName name="tol" localSheetId="0">'[28]규모,공수분석'!#REF!</definedName>
+    <definedName name="tol" localSheetId="0">'[25]규모,공수분석'!#REF!</definedName>
     <definedName name="TOTAL" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="US" localSheetId="0">[23]COST!$P$2</definedName>
     <definedName name="vbkjwhe" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -599,103 +696,6 @@
     <definedName name="wrn.aaa." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="wrn.TEST." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="wte" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="계획표" localSheetId="0">#REF!</definedName>
-    <definedName name="공사설명서" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업" localSheetId="0">[23]COST!#REF!</definedName>
-    <definedName name="과업대비표1" localSheetId="0">#REF!</definedName>
-    <definedName name="국소수_서울" localSheetId="0">#REF!</definedName>
-    <definedName name="기존프로그램" localSheetId="0">#REF!</definedName>
-    <definedName name="ㄴㄴ" localSheetId="0">[25]단계별측정!#REF!</definedName>
-    <definedName name="ㄴㄴㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴ아러" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="나" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="납기1" localSheetId="0">[26]IN!$B$5</definedName>
-    <definedName name="납기2" localSheetId="0">[27]IN!$B$5</definedName>
-    <definedName name="납기3" localSheetId="0">[26]IN!$D$5</definedName>
-    <definedName name="납기4" localSheetId="0">[27]IN!$D$5</definedName>
-    <definedName name="ㄷ가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="두지" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="둑ㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄹㅇㅁㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="라" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄻㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㄻㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㅁㅁ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="마" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="문서번호표시" localSheetId="0">"Document #: " &amp; DocumentName</definedName>
-    <definedName name="ㅂㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="바" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="버전" localSheetId="0">"Version " &amp; Version</definedName>
-    <definedName name="변경내역" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="보" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="사" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정2" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정3" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정4" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정5" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정6" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="신설변경" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇ나닐ㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㄹㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㄹㅈㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㅀㅇㅁㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㅇㄹㅈㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇ아" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="아" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ지" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅗㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="이름" localSheetId="0" hidden="1">#REF!</definedName>
-    <definedName name="이름1" localSheetId="0">#REF!</definedName>
-    <definedName name="일반현황__2_" localSheetId="0">#REF!</definedName>
-    <definedName name="일일대가1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="잊" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈㅂㄷㅈㅂㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자ㅓㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="정" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="제주추가종합수정안" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="지더" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="지두" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="차" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="총괄11" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅋㅋ" localSheetId="0">[25]단계별측정!#REF!</definedName>
-    <definedName name="ㅋㅋㅋ" localSheetId="0">#REF!</definedName>
-    <definedName name="카" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="타" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="특별시방서1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="파" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="하" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="한" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="홎ㅅㄱ도" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ딪" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ잊" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ짇" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄴ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅓ아ㅣㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜㅈ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ자ㅣㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ닺" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅈ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ잗" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ젇" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="_" localSheetId="1">#REF!</definedName>
     <definedName name="__" localSheetId="1">#REF!</definedName>
     <definedName name="_80486SX_25" localSheetId="1">[1]COST!#REF!</definedName>
@@ -704,6 +704,96 @@
     <definedName name="_Table1_Out" localSheetId="1" hidden="1">#REF!</definedName>
     <definedName name="_wo1" localSheetId="1">'[2]예정(3)'!#REF!</definedName>
     <definedName name="\0" localSheetId="1">'[3]9GNG운반'!#REF!</definedName>
+    <definedName name="ㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="가" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="계획표" localSheetId="1">#REF!</definedName>
+    <definedName name="공사설명서" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="과업" localSheetId="1">[23]COST!#REF!</definedName>
+    <definedName name="과업대비표1" localSheetId="1">#REF!</definedName>
+    <definedName name="국소수_서울" localSheetId="1">#REF!</definedName>
+    <definedName name="기존프로그램" localSheetId="1">#REF!</definedName>
+    <definedName name="ㄴㄴ" localSheetId="1">[32]단계별측정!#REF!</definedName>
+    <definedName name="ㄴㄴㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴ아러" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="나" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄷ가" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="두지" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="둑ㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄹㅇㅁㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="라" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅁㅁㅁ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="마" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="문서번호표시" localSheetId="1">"Document #: " &amp; DocumentName</definedName>
+    <definedName name="ㅁㄻㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅂㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="바" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="버전" localSheetId="1">"Version " &amp; Version</definedName>
+    <definedName name="변경내역" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="보" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="사" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정2" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정3" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정4" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정5" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정6" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="신설변경" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇ나닐ㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㄹㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㄹㅈㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㅇㄹㅈㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇ아" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㅀㅇㅁㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="아" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ지" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅗㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="일일대가1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="잊" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈㅂㄷㅈㅂㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자ㅓㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="정" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="제주추가종합수정안" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="지더" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="지두" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="차" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="총괄11" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅋㅋ" localSheetId="1">[32]단계별측정!#REF!</definedName>
+    <definedName name="ㅋㅋㅋ" localSheetId="1">#REF!</definedName>
+    <definedName name="카" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="타" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="특별시방서1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="파" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="하" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="한" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="홎ㅅㄱ도" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ딪" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ잊" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ짇" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄴ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅓ아ㅣㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜㅈ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ자ㅣㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ닺" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅈ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ잗" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ젇" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄻㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="A" localSheetId="1">#REF!</definedName>
     <definedName name="A000" localSheetId="1">#REF!</definedName>
     <definedName name="a2121212" localSheetId="1">'[3]9GNG운반'!#REF!</definedName>
@@ -755,8 +845,8 @@
     <definedName name="IT_A" localSheetId="1">IF( OR(AND(#REF!&lt;2,#REF!&gt;15), AND(#REF!=2, AND(#REF!&gt;= 5,#REF!&lt;= 15)), AND(#REF!&gt;2, AND(#REF!&gt;=1,#REF!&lt;= 4)) ),1,0)</definedName>
     <definedName name="IT_C" localSheetId="1">IF( OR(AND(#REF!=2,#REF!&gt; 15), AND(#REF!&gt;2,#REF!&gt;=  5) ),1,0)</definedName>
     <definedName name="IT_S" localSheetId="1">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 15)), AND(#REF!=2, AND(#REF!&gt;= 1,#REF!&lt;= 4)) ),1,0)</definedName>
-    <definedName name="itsa_ratio_nrec" localSheetId="1">[22]공수견적!#REF!</definedName>
-    <definedName name="itsa_ratio_rec" localSheetId="1">[20]순수개발!#REF!</definedName>
+    <definedName name="itsa_ratio_nrec" localSheetId="1">[9]공수견적!#REF!</definedName>
+    <definedName name="itsa_ratio_rec" localSheetId="1">[7]순수개발!#REF!</definedName>
     <definedName name="IWFIC" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jdkl" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jeklw" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -831,116 +921,25 @@
     <definedName name="wrn.aaa." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="wrn.TEST." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="wte" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="가" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="계획표" localSheetId="1">#REF!</definedName>
-    <definedName name="공사설명서" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업" localSheetId="1">[23]COST!#REF!</definedName>
-    <definedName name="과업대비표1" localSheetId="1">#REF!</definedName>
-    <definedName name="국소수_서울" localSheetId="1">#REF!</definedName>
-    <definedName name="기존프로그램" localSheetId="1">#REF!</definedName>
-    <definedName name="ㄴㄴ" localSheetId="1">[25]단계별측정!#REF!</definedName>
-    <definedName name="ㄴㄴㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴ아러" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="나" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄷ가" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="두지" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="둑ㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄹㅇㅁㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="라" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄻㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㄻㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㅁㅁ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="마" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="문서번호표시" localSheetId="1">"Document #: " &amp; DocumentName</definedName>
-    <definedName name="ㅂㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="바" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="버전" localSheetId="1">"Version " &amp; Version</definedName>
-    <definedName name="변경내역" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="보" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="사" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정2" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정3" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정4" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정5" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정6" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="신설변경" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇ나닐ㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㄹㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㄹㅈㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㅀㅇㅁㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㅇㄹㅈㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇ아" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="아" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ지" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅗㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="일일대가1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="잊" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈㅂㄷㅈㅂㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자ㅓㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="정" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="제주추가종합수정안" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="지더" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="지두" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="차" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="총괄11" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅋㅋ" localSheetId="1">[25]단계별측정!#REF!</definedName>
-    <definedName name="ㅋㅋㅋ" localSheetId="1">#REF!</definedName>
-    <definedName name="카" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="타" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="특별시방서1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="파" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="하" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="한" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="홎ㅅㄱ도" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ딪" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ잊" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ짇" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄴ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅓ아ㅣㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜㅈ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ자ㅣㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ닺" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅈ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ잗" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ젇" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
   </definedNames>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
-    <numFmt numFmtId="164" formatCode="yyyy\.mm\.dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00_);&quot;₩&quot;&quot;₩&quot;\(&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\)"/>
-    <numFmt numFmtId="168" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="&quot;₩&quot;#,##0;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;₩&quot;* #,##0_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="173" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="9">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00_);&quot;₩&quot;&quot;₩&quot;\(&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\$#,##0.00&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\)"/>
+    <numFmt numFmtId="167" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="&quot;₩&quot;#,##0;[Red]&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;₩&quot;* #,##0_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="172" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="65">
+  <fonts count="63">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -1386,22 +1385,6 @@
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="28"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
       <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
@@ -1416,15 +1399,15 @@
       <name val="맑은 고딕"/>
       <charset val="129"/>
       <family val="2"/>
-      <color rgb="FF999999"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="14"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="39">
@@ -1642,7 +1625,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="46">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1875,103 +1858,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1993,99 +1879,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2137,46 +1930,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1645">
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
@@ -2189,14 +1942,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="7" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2210,7 +1963,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="10" fontId="7" fillId="2" borderId="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -4815,14 +4568,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4961,33 +4714,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5015,90 +4752,41 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -5137,63 +4825,27 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1643"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1476">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1643"/>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1643">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7020,6 +6672,82 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="산출"/>
+      <sheetName val="OUT"/>
+      <sheetName val="IN"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="COST"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="1.갑지"/>
+      <sheetName val="2.개정이력"/>
+      <sheetName val="3.요구사항기술"/>
+      <sheetName val="검증자료"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="단계별측정"/>
+      <sheetName val="프로젝트정보"/>
+      <sheetName val="크기추정"/>
+      <sheetName val="공수추정"/>
+      <sheetName val="검토측정"/>
+      <sheetName val="변경측정"/>
+      <sheetName val="문서크기측정"/>
+      <sheetName val="소스코드크기측정"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
       <sheetName val="IN"/>
     </sheetNames>
     <sheetDataSet>
@@ -7029,7 +6757,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7060,7 +6788,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7089,7 +6817,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7120,7 +6848,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7149,7 +6877,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7175,100 +6903,6 @@
       <sheetData sheetId="7" refreshError="1"/>
       <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="작성정보"/>
-      <sheetName val="사용안내"/>
-      <sheetName val="업무절차설계도"/>
-      <sheetName val="업무활동"/>
-      <sheetName val="정보흐름"/>
-      <sheetName val="조직(참고)"/>
-      <sheetName val="응용시스템(참고)"/>
-      <sheetName val="공통코드"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="main"/>
-      <sheetName val="DATA"/>
-      <sheetName val="ELEC"/>
-      <sheetName val="Raw"/>
-      <sheetName val="발생"/>
-      <sheetName val="평가"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="표지"/>
-      <sheetName val="응용시스템구성도"/>
-      <sheetName val="응용도메인"/>
-      <sheetName val="응용시스템"/>
-      <sheetName val="응용시스템-응용시스템"/>
-      <sheetName val="응용도메인_업무대기능"/>
-      <sheetName val="응용시스템_업무중기능_위치_데이터베이스"/>
-      <sheetName val="조사표항목설명"/>
-      <sheetName val="공통코드"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Calc V1.2 (2)"/>
-      <sheetName val="Calc V1.2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7341,26 +6975,65 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="ILF &amp; EIF"/>
-      <sheetName val="EI"/>
-      <sheetName val="EQ"/>
-      <sheetName val="EO"/>
-      <sheetName val="FPA"/>
-      <sheetName val="Package (In-House)"/>
-      <sheetName val="In House"/>
-      <sheetName val="VAF"/>
-      <sheetName val="순수개발"/>
-      <sheetName val="Macro상수지정"/>
-      <sheetName val="Config"/>
-      <sheetName val="Package (by ITSA)"/>
-      <sheetName val="Dialog1"/>
-      <sheetName val="Module1"/>
-      <sheetName val="Module2"/>
-      <sheetName val="영남_1"/>
-      <sheetName val="견적990322"/>
-      <sheetName val="20관리비율"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="노임"/>
+      <sheetName val="작성정보"/>
+      <sheetName val="사용안내"/>
+      <sheetName val="업무절차설계도"/>
+      <sheetName val="업무활동"/>
+      <sheetName val="정보흐름"/>
+      <sheetName val="조직(참고)"/>
+      <sheetName val="응용시스템(참고)"/>
+      <sheetName val="공통코드"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="main"/>
+      <sheetName val="DATA"/>
+      <sheetName val="ELEC"/>
+      <sheetName val="Raw"/>
+      <sheetName val="발생"/>
+      <sheetName val="평가"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="표지"/>
+      <sheetName val="응용시스템구성도"/>
+      <sheetName val="응용도메인"/>
+      <sheetName val="응용시스템"/>
+      <sheetName val="응용시스템-응용시스템"/>
+      <sheetName val="응용도메인_업무대기능"/>
+      <sheetName val="응용시스템_업무중기능_위치_데이터베이스"/>
+      <sheetName val="조사표항목설명"/>
+      <sheetName val="공통코드"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -7372,75 +7045,6 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="fpa_dev(dev)"/>
-      <sheetName val="Data Vol"/>
-      <sheetName val="FPA"/>
-      <sheetName val="순수개발"/>
-      <sheetName val="ilch"/>
-      <sheetName val="Galaxy 소비자가격표"/>
-      <sheetName val="공사내역"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="개정이력"/>
-      <sheetName val="기본정보"/>
-      <sheetName val="Data"/>
-      <sheetName val="Transaction"/>
-      <sheetName val="FPA_검증"/>
-      <sheetName val="VAF"/>
-      <sheetName val="공수견적"/>
-      <sheetName val="비용산정"/>
-      <sheetName val="품질항목"/>
-      <sheetName val="CountingTip"/>
-      <sheetName val="Macro상수"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7489,205 +7093,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="프로젝트정보"/>
-      <sheetName val="크기추정"/>
-      <sheetName val="공수추정"/>
-      <sheetName val="단계별측정"/>
-      <sheetName val="검토측정"/>
-      <sheetName val="변경측정"/>
-      <sheetName val="문서크기측정"/>
-      <sheetName val="소스코드크기측정"/>
-      <sheetName val="개정이력"/>
-      <sheetName val="기본정보"/>
-      <sheetName val="Data"/>
-      <sheetName val="Transaction"/>
-      <sheetName val="FPA_검증"/>
-      <sheetName val="VAF"/>
-      <sheetName val="공수견적"/>
-      <sheetName val="비용산정"/>
-      <sheetName val="품질항목"/>
-      <sheetName val="CountingTip"/>
-      <sheetName val="Macro상수"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="산출"/>
-      <sheetName val="OUT"/>
-      <sheetName val="IN"/>
-      <sheetName val="ILF &amp; EIF"/>
-      <sheetName val="EI"/>
-      <sheetName val="EQ"/>
-      <sheetName val="EO"/>
-      <sheetName val="FPA"/>
-      <sheetName val="Package (In-House)"/>
-      <sheetName val="In House"/>
-      <sheetName val="VAF"/>
-      <sheetName val="순수개발"/>
-      <sheetName val="Macro상수지정"/>
-      <sheetName val="Config"/>
-      <sheetName val="Package (by ITSA)"/>
-      <sheetName val="Dialog1"/>
-      <sheetName val="Module1"/>
-      <sheetName val="Module2"/>
-      <sheetName val="영남_1"/>
-      <sheetName val="견적990322"/>
-      <sheetName val="20관리비율"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="노임"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="IN"/>
-      <sheetName val="요약"/>
-      <sheetName val="SIZE"/>
-      <sheetName val="SIZE_DETAIL"/>
-      <sheetName val="운영현황보고(5월)"/>
-      <sheetName val="Summary"/>
-      <sheetName val="유형별CSR처리현황"/>
-      <sheetName val="주별 CSR 처리현황"/>
-      <sheetName val="유형별 CSR 분석(모듈)"/>
-      <sheetName val="SAP등록 건 확인(5월)"/>
-      <sheetName val="규모,공수분석"/>
-      <sheetName val="기타 공수분석"/>
-      <sheetName val="CCR(최대CPU사용율)"/>
-      <sheetName val="CCR(평균CPU사용율)"/>
-      <sheetName val="CCR(최대PAGING SPACE IO"/>
-      <sheetName val="CCR(평균PAGING SPACE IO"/>
-      <sheetName val="CCR(디스크사용량)"/>
-      <sheetName val="CCE(디스크사용량_DATA)"/>
-      <sheetName val="CSR납기분석"/>
-      <sheetName val="결함분석(누적)"/>
-      <sheetName val="inspection_data(5월)"/>
-      <sheetName val="Inspection summary"/>
-      <sheetName val="위험문제관리"/>
-      <sheetName val="Test"/>
-      <sheetName val="구성관리(실적)"/>
-      <sheetName val="SQA"/>
-      <sheetName val="교육"/>
-      <sheetName val="2003년도_교육계획(안)"/>
-      <sheetName val="08.Lessons Learned"/>
-      <sheetName val="1.요약"/>
-      <sheetName val="2.일정추적"/>
-      <sheetName val="3.규모추적"/>
-      <sheetName val="4.1공수분석_개발"/>
-      <sheetName val="4.2공수추적_관리"/>
-      <sheetName val="5.1결함분석_현황"/>
-      <sheetName val="5.2결함분석_제거"/>
-      <sheetName val="6.Risks"/>
-      <sheetName val="7.실시내용 &amp; Issues"/>
-      <sheetName val="8.Lessons"/>
-      <sheetName val="99.1공수"/>
-      <sheetName val="99.2결함"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7768,7 +7173,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7789,20 +7194,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="9GNG운반"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7855,7 +7247,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7934,7 +7326,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7971,7 +7363,77 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="9GNG운반"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="산출"/>
+      <sheetName val="OUT"/>
+      <sheetName val="IN"/>
+      <sheetName val="ILF &amp; EIF"/>
+      <sheetName val="EI"/>
+      <sheetName val="EQ"/>
+      <sheetName val="EO"/>
+      <sheetName val="FPA"/>
+      <sheetName val="Package (In-House)"/>
+      <sheetName val="In House"/>
+      <sheetName val="VAF"/>
+      <sheetName val="순수개발"/>
+      <sheetName val="Macro상수지정"/>
+      <sheetName val="Config"/>
+      <sheetName val="Package (by ITSA)"/>
+      <sheetName val="Dialog1"/>
+      <sheetName val="Module1"/>
+      <sheetName val="Module2"/>
+      <sheetName val="영남_1"/>
+      <sheetName val="견적990322"/>
+      <sheetName val="20관리비율"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="노임"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -8071,6 +7533,148 @@
       <sheetData sheetId="44" refreshError="1"/>
       <sheetData sheetId="45" refreshError="1"/>
       <sheetData sheetId="46" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="프로젝트정보"/>
+      <sheetName val="크기추정"/>
+      <sheetName val="공수추정"/>
+      <sheetName val="단계별측정"/>
+      <sheetName val="검토측정"/>
+      <sheetName val="변경측정"/>
+      <sheetName val="문서크기측정"/>
+      <sheetName val="소스코드크기측정"/>
+      <sheetName val="개정이력"/>
+      <sheetName val="기본정보"/>
+      <sheetName val="Data"/>
+      <sheetName val="Transaction"/>
+      <sheetName val="FPA_검증"/>
+      <sheetName val="VAF"/>
+      <sheetName val="공수견적"/>
+      <sheetName val="비용산정"/>
+      <sheetName val="품질항목"/>
+      <sheetName val="CountingTip"/>
+      <sheetName val="Macro상수"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="IN"/>
+      <sheetName val="요약"/>
+      <sheetName val="SIZE"/>
+      <sheetName val="SIZE_DETAIL"/>
+      <sheetName val="운영현황보고(5월)"/>
+      <sheetName val="Summary"/>
+      <sheetName val="유형별CSR처리현황"/>
+      <sheetName val="주별 CSR 처리현황"/>
+      <sheetName val="유형별 CSR 분석(모듈)"/>
+      <sheetName val="SAP등록 건 확인(5월)"/>
+      <sheetName val="규모,공수분석"/>
+      <sheetName val="기타 공수분석"/>
+      <sheetName val="CCR(최대CPU사용율)"/>
+      <sheetName val="CCR(평균CPU사용율)"/>
+      <sheetName val="CCR(최대PAGING SPACE IO"/>
+      <sheetName val="CCR(평균PAGING SPACE IO"/>
+      <sheetName val="CCR(디스크사용량)"/>
+      <sheetName val="CCE(디스크사용량_DATA)"/>
+      <sheetName val="CSR납기분석"/>
+      <sheetName val="결함분석(누적)"/>
+      <sheetName val="inspection_data(5월)"/>
+      <sheetName val="Inspection summary"/>
+      <sheetName val="위험문제관리"/>
+      <sheetName val="Test"/>
+      <sheetName val="구성관리(실적)"/>
+      <sheetName val="SQA"/>
+      <sheetName val="교육"/>
+      <sheetName val="2003년도_교육계획(안)"/>
+      <sheetName val="08.Lessons Learned"/>
+      <sheetName val="1.요약"/>
+      <sheetName val="2.일정추적"/>
+      <sheetName val="3.규모추적"/>
+      <sheetName val="4.1공수분석_개발"/>
+      <sheetName val="4.2공수추적_관리"/>
+      <sheetName val="5.1결함분석_현황"/>
+      <sheetName val="5.2결함분석_제거"/>
+      <sheetName val="6.Risks"/>
+      <sheetName val="7.실시내용 &amp; Issues"/>
+      <sheetName val="8.Lessons"/>
+      <sheetName val="99.1공수"/>
+      <sheetName val="99.2결함"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -8236,33 +7840,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="프로젝트정보"/>
-      <sheetName val="크기추정"/>
-      <sheetName val="공수추정"/>
-      <sheetName val="단계별측정"/>
-      <sheetName val="검토측정"/>
-      <sheetName val="변경측정"/>
-      <sheetName val="문서크기측정"/>
-      <sheetName val="소스코드크기측정"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="작성정보"/>
       <sheetName val="사용안내"/>
       <sheetName val="응용기능분할도"/>
@@ -8294,53 +7871,21 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="COST"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="1.갑지"/>
-      <sheetName val="2.개정이력"/>
-      <sheetName val="3.요구사항기술"/>
-      <sheetName val="검증자료"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="단계별측정"/>
       <sheetName val="프로젝트정보"/>
       <sheetName val="크기추정"/>
       <sheetName val="공수추정"/>
+      <sheetName val="단계별측정"/>
       <sheetName val="검토측정"/>
       <sheetName val="변경측정"/>
       <sheetName val="문서크기측정"/>
       <sheetName val="소스코드크기측정"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
@@ -8353,18 +7898,125 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="산출"/>
-      <sheetName val="OUT"/>
-      <sheetName val="IN"/>
+      <sheetName val="Calc V1.2 (2)"/>
+      <sheetName val="Calc V1.2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="ILF &amp; EIF"/>
+      <sheetName val="EI"/>
+      <sheetName val="EQ"/>
+      <sheetName val="EO"/>
+      <sheetName val="FPA"/>
+      <sheetName val="Package (In-House)"/>
+      <sheetName val="In House"/>
+      <sheetName val="VAF"/>
+      <sheetName val="순수개발"/>
+      <sheetName val="Macro상수지정"/>
+      <sheetName val="Config"/>
+      <sheetName val="Package (by ITSA)"/>
+      <sheetName val="Dialog1"/>
+      <sheetName val="Module1"/>
+      <sheetName val="Module2"/>
+      <sheetName val="영남_1"/>
+      <sheetName val="견적990322"/>
+      <sheetName val="20관리비율"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="노임"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="fpa_dev(dev)"/>
+      <sheetName val="Data Vol"/>
+      <sheetName val="FPA"/>
+      <sheetName val="순수개발"/>
+      <sheetName val="ilch"/>
+      <sheetName val="Galaxy 소비자가격표"/>
+      <sheetName val="공사내역"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="개정이력"/>
+      <sheetName val="기본정보"/>
+      <sheetName val="Data"/>
+      <sheetName val="Transaction"/>
+      <sheetName val="FPA_검증"/>
+      <sheetName val="VAF"/>
+      <sheetName val="공수견적"/>
+      <sheetName val="비용산정"/>
+      <sheetName val="품질항목"/>
+      <sheetName val="CountingTip"/>
+      <sheetName val="Macro상수"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -8662,122 +8314,122 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:I30"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.375" defaultRowHeight="17.1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="17"/>
   <cols>
-    <col width="8.125" customWidth="1" style="54" min="1" max="1"/>
-    <col width="4.875" customWidth="1" style="54" min="2" max="2"/>
-    <col width="12.375" customWidth="1" style="54" min="3" max="4"/>
-    <col width="4.125" customWidth="1" style="54" min="5" max="5"/>
-    <col width="4.625" customWidth="1" style="54" min="6" max="6"/>
-    <col width="13.125" customWidth="1" style="54" min="7" max="7"/>
-    <col width="10.5" customWidth="1" style="54" min="8" max="8"/>
-    <col width="9" customWidth="1" style="54" min="9" max="9"/>
-    <col width="11.375" customWidth="1" style="54" min="10" max="13"/>
-    <col width="11.375" customWidth="1" style="54" min="14" max="16384"/>
+    <col width="8.1640625" customWidth="1" style="27" min="1" max="1"/>
+    <col width="4.83203125" customWidth="1" style="27" min="2" max="2"/>
+    <col width="12.33203125" customWidth="1" style="27" min="3" max="4"/>
+    <col width="4.1640625" customWidth="1" style="27" min="5" max="5"/>
+    <col width="4.6640625" customWidth="1" style="27" min="6" max="6"/>
+    <col width="13.1640625" customWidth="1" style="27" min="7" max="7"/>
+    <col width="10.5" customWidth="1" style="27" min="8" max="8"/>
+    <col width="9" customWidth="1" style="27" min="9" max="9"/>
+    <col width="11.33203125" customWidth="1" style="27" min="10" max="14"/>
+    <col width="11.33203125" customWidth="1" style="27" min="15" max="16384"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.6" customHeight="1" s="48">
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="56" t="inlineStr">
+    <row r="2" ht="27.5" customHeight="1" s="46">
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="29" t="inlineStr">
         <is>
           <t>문서관리번호</t>
         </is>
       </c>
-      <c r="G2" s="57" t="n"/>
-      <c r="H2" s="59" t="inlineStr">
+      <c r="G2" s="30" t="n"/>
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>버전</t>
         </is>
       </c>
-      <c r="I2" s="57" t="n"/>
+      <c r="I2" s="30" t="n"/>
     </row>
-    <row r="3" ht="27.6" customHeight="1" s="48">
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="58" t="inlineStr">
+    <row r="3" ht="27.5" customHeight="1" s="46">
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="31" t="inlineStr">
         <is>
           <t>JJ_PD_IP_D27</t>
         </is>
       </c>
-      <c r="G3" s="57" t="n"/>
-      <c r="H3" s="64" t="inlineStr">
+      <c r="G3" s="30" t="n"/>
+      <c r="H3" s="37" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="I3" s="65" t="n"/>
+      <c r="I3" s="38" t="n"/>
     </row>
-    <row r="9" ht="26.25" customHeight="1" s="48">
-      <c r="A9" s="63" t="inlineStr">
+    <row r="9" ht="26.25" customHeight="1" s="46">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>'25년 제주스마트도시 데이터허브 시범솔루션 발굴사업</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="9.6" customHeight="1" s="48">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
+    <row r="10" ht="9.5" customHeight="1" s="46">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
     </row>
-    <row r="11" ht="50.25" customHeight="1" s="48">
-      <c r="A11" s="60" t="inlineStr">
+    <row r="11" ht="50.25" customHeight="1" s="46">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>통합테스트 계획서</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="1.5" customHeight="1" s="48">
-      <c r="A12" s="13" t="n"/>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="13" t="n"/>
+    <row r="12" ht="1.5" customHeight="1" s="46">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
     </row>
-    <row r="13" ht="9.6" customHeight="1" s="48">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
+    <row r="13" ht="9.5" customHeight="1" s="46">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
     </row>
-    <row r="14" ht="24.75" customHeight="1" s="48">
-      <c r="A14" s="62" t="inlineStr">
+    <row r="14" ht="24.75" customHeight="1" s="46">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>AI주차민원솔루션</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="43.5" customHeight="1" s="48">
-      <c r="B28" s="55" t="n"/>
-      <c r="E28" s="55" t="n"/>
-      <c r="F28" s="61" t="n"/>
+    <row r="28" ht="43.5" customHeight="1" s="46">
+      <c r="B28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="34" t="n"/>
     </row>
-    <row r="29" ht="43.5" customHeight="1" s="48">
-      <c r="B29" s="61" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="E29" s="61" t="n"/>
-      <c r="F29" s="61" t="n"/>
-      <c r="G29" s="53" t="n"/>
+    <row r="29" ht="43.5" customHeight="1" s="46">
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="34" t="n"/>
+      <c r="G29" s="26" t="n"/>
     </row>
-    <row r="30" ht="43.5" customHeight="1" s="48">
-      <c r="B30" s="61" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="E30" s="61" t="n"/>
-      <c r="F30" s="61" t="n"/>
-      <c r="G30" s="53" t="n"/>
+    <row r="30" ht="43.5" customHeight="1" s="46">
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="34" t="n"/>
+      <c r="G30" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -8785,12 +8437,12 @@
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G30:H30"/>
     <mergeCell ref="A11:I11"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C29:D29"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="H3:I3"/>
@@ -8809,291 +8461,269 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:E30"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.375" defaultRowHeight="17.1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="17"/>
   <cols>
-    <col width="15.125" customWidth="1" style="84" min="1" max="1"/>
-    <col width="10.625" customWidth="1" style="84" min="2" max="2"/>
-    <col width="57.5" customWidth="1" style="84" min="3" max="3"/>
-    <col width="10.5" customWidth="1" style="84" min="4" max="5"/>
-    <col width="11.375" customWidth="1" style="84" min="6" max="9"/>
-    <col width="11.375" customWidth="1" style="84" min="10" max="16384"/>
+    <col width="15.1640625" customWidth="1" style="40" min="1" max="1"/>
+    <col width="10.6640625" customWidth="1" style="40" min="2" max="2"/>
+    <col width="57.5" customWidth="1" style="40" min="3" max="3"/>
+    <col width="10.5" customWidth="1" style="40" min="4" max="5"/>
+    <col width="11.33203125" customWidth="1" style="40" min="6" max="10"/>
+    <col width="11.33203125" customWidth="1" style="40" min="11" max="16384"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26.25" customHeight="1" s="48">
-      <c r="A2" s="66" t="inlineStr">
+    <row r="2" ht="26.25" customHeight="1" s="46">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>개 정 이 력</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24.75" customHeight="1" s="48">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="24.75" customHeight="1" s="46">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>제 개정일자</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>버전</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>제 개정내용</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>작성자</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>승인자</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24.75" customHeight="1" s="48">
-      <c r="A5" s="17" t="inlineStr">
+    <row r="5" ht="24.75" customHeight="1" s="46">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>최초작성</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>함현진</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>박규영</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="72" customHeight="1" s="48">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>v1.4</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>하단 화면설계(D04) 점검 블록을 해당 시나리오 내부로 통합 배치(같은 화면 기준 인접) / 통합된 화면 점검 행은 셀 색상(파랑)·변경구분 「화면설계」로 구분 / 프로그램 ID 미정의 화면은 공란 유지</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
+    <row r="6" ht="72" customHeight="1" s="46">
+      <c r="A6" s="48" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>개발 현행화</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>박규영</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>박규영</t>
+        </is>
+      </c>
     </row>
-    <row r="7" ht="24.75" customHeight="1" s="48">
-      <c r="A7" s="86" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>v1.2</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>개발 결과 현행화: 로그인(D-Hub 통합 인증), 민원현황 히트맵 표현 전환, 정책 변수(예측 기간 삭제·확충 방식), 구역추천(증가 추세 반영·산정 기준 ⓘ), AI 조례 응답(조문 발췌), 설정(메뉴 권한 관리) 반영</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>이노팸</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
+    <row r="7" ht="24.75" customHeight="1" s="46">
+      <c r="A7" s="49" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
     </row>
-    <row r="8" ht="24.75" customHeight="1" s="48">
-      <c r="A8" s="86" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>계획서·결과서 분리(기존 M06 v1.2에서 계획서 분책)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>이노팸</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr"/>
+    <row r="8" ht="24.75" customHeight="1" s="46">
+      <c r="A8" s="49" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
     </row>
-    <row r="9" ht="24.75" customHeight="1" s="48">
-      <c r="A9" s="17" t="n"/>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
+    <row r="9" ht="24.75" customHeight="1" s="46">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
     </row>
-    <row r="10" ht="24.75" customHeight="1" s="48">
-      <c r="A10" s="17" t="n"/>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
+    <row r="10" ht="24.75" customHeight="1" s="46">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
     </row>
-    <row r="11" ht="24.75" customHeight="1" s="48">
-      <c r="A11" s="17" t="n"/>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
+    <row r="11" ht="24.75" customHeight="1" s="46">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
     </row>
-    <row r="12" ht="24.75" customHeight="1" s="48">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
+    <row r="12" ht="24.75" customHeight="1" s="46">
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
     </row>
-    <row r="13" ht="24.75" customHeight="1" s="48">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
+    <row r="13" ht="24.75" customHeight="1" s="46">
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
     </row>
-    <row r="14" ht="24.75" customHeight="1" s="48">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
+    <row r="14" ht="24.75" customHeight="1" s="46">
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
     </row>
-    <row r="15" ht="24.75" customHeight="1" s="48">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
+    <row r="15" ht="24.75" customHeight="1" s="46">
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
     </row>
-    <row r="16" ht="24.75" customHeight="1" s="48">
-      <c r="A16" s="17" t="n"/>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
+    <row r="16" ht="24.75" customHeight="1" s="46">
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
     </row>
-    <row r="17" ht="24.75" customHeight="1" s="48">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
+    <row r="17" ht="24.75" customHeight="1" s="46">
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
     </row>
-    <row r="18" ht="24.75" customHeight="1" s="48">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+    <row r="18" ht="24.75" customHeight="1" s="46">
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
     </row>
-    <row r="19" ht="24.75" customHeight="1" s="48">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+    <row r="19" ht="24.75" customHeight="1" s="46">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
     </row>
-    <row r="20" ht="24.75" customHeight="1" s="48">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+    <row r="20" ht="24.75" customHeight="1" s="46">
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
     </row>
-    <row r="21" ht="24.75" customHeight="1" s="48">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+    <row r="21" ht="24.75" customHeight="1" s="46">
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
     </row>
-    <row r="22" ht="24.75" customHeight="1" s="48">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+    <row r="22" ht="24.75" customHeight="1" s="46">
+      <c r="A22" s="12" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
     </row>
-    <row r="23" ht="24.75" customHeight="1" s="48">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+    <row r="23" ht="24.75" customHeight="1" s="46">
+      <c r="A23" s="12" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
     </row>
-    <row r="24" ht="24.75" customHeight="1" s="48">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+    <row r="24" ht="24.75" customHeight="1" s="46">
+      <c r="A24" s="12" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
     </row>
-    <row r="25" ht="24.75" customHeight="1" s="48">
-      <c r="A25" s="17" t="n"/>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+    <row r="25" ht="24.75" customHeight="1" s="46">
+      <c r="A25" s="12" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
     </row>
-    <row r="26" ht="24.75" customHeight="1" s="48">
-      <c r="A26" s="17" t="n"/>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
+    <row r="26" ht="24.75" customHeight="1" s="46">
+      <c r="A26" s="12" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
     </row>
-    <row r="27" ht="24.75" customHeight="1" s="48">
-      <c r="A27" s="17" t="n"/>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
+    <row r="27" ht="24.75" customHeight="1" s="46">
+      <c r="A27" s="12" t="n"/>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
     </row>
-    <row r="28" ht="24.75" customHeight="1" s="48">
-      <c r="A28" s="17" t="n"/>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
+    <row r="28" ht="24.75" customHeight="1" s="46">
+      <c r="A28" s="12" t="n"/>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
     </row>
-    <row r="29" ht="24.75" customHeight="1" s="48">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
+    <row r="29" ht="24.75" customHeight="1" s="46">
+      <c r="A29" s="12" t="n"/>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
     </row>
-    <row r="30" ht="24.75" customHeight="1" s="48">
-      <c r="A30" s="17" t="n"/>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
+    <row r="30" ht="24.75" customHeight="1" s="46">
+      <c r="A30" s="12" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9120,153 +8750,153 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:M58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="5.5" customWidth="1" style="48" min="1" max="1"/>
-    <col width="12" customWidth="1" style="48" min="2" max="2"/>
-    <col width="30" customWidth="1" style="48" min="3" max="3"/>
-    <col width="14" customWidth="1" style="48" min="4" max="5"/>
-    <col width="26" customWidth="1" style="48" min="6" max="6"/>
-    <col width="20" customWidth="1" style="48" min="7" max="7"/>
-    <col width="14" customWidth="1" style="48" min="8" max="8"/>
-    <col width="26" customWidth="1" style="48" min="9" max="9"/>
-    <col width="66" customWidth="1" style="48" min="10" max="10"/>
-    <col width="20" customWidth="1" style="48" min="11" max="11"/>
-    <col width="52" customWidth="1" style="48" min="12" max="12"/>
-    <col width="13" customWidth="1" style="48" min="13" max="13"/>
+    <col width="5.5" customWidth="1" style="46" min="1" max="1"/>
+    <col width="12" customWidth="1" style="46" min="2" max="2"/>
+    <col width="30" customWidth="1" style="46" min="3" max="3"/>
+    <col width="14" customWidth="1" style="46" min="4" max="5"/>
+    <col width="26" customWidth="1" style="46" min="6" max="6"/>
+    <col width="20" customWidth="1" style="46" min="7" max="7"/>
+    <col width="14" customWidth="1" style="46" min="8" max="8"/>
+    <col width="26" customWidth="1" style="46" min="9" max="9"/>
+    <col width="66" customWidth="1" style="46" min="10" max="10"/>
+    <col width="20" customWidth="1" style="46" min="11" max="11"/>
+    <col width="52" customWidth="1" style="46" min="12" max="12"/>
+    <col width="13" customWidth="1" style="46" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="2" ht="41.25" customHeight="1" s="48">
-      <c r="A2" s="72" t="inlineStr">
+    <row r="2" ht="41.25" customHeight="1" s="46">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>통합테스트계획서_AI 주차민원 분석 솔루션</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.95" customHeight="1" s="48">
-      <c r="A4" s="70" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="46">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B4" s="70" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>시나리오 ID</t>
         </is>
       </c>
-      <c r="C4" s="70" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>업무 흐름</t>
         </is>
       </c>
-      <c r="D4" s="70" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>주 수행 그룹</t>
         </is>
       </c>
-      <c r="E4" s="70" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>통합테스트 ID</t>
         </is>
       </c>
-      <c r="F4" s="70" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>통합테스트명</t>
         </is>
       </c>
-      <c r="G4" s="70" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>프로그램 ID</t>
         </is>
       </c>
-      <c r="H4" s="70" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>화면 ID</t>
         </is>
       </c>
-      <c r="I4" s="70" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>시나리오명</t>
         </is>
       </c>
-      <c r="J4" s="70" t="inlineStr">
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>테스트 상세설명</t>
         </is>
       </c>
-      <c r="K4" s="70" t="inlineStr">
+      <c r="K4" s="41" t="inlineStr">
         <is>
           <t>테스트데이터 
 or 확인 코멘트</t>
         </is>
       </c>
-      <c r="L4" s="70" t="inlineStr">
+      <c r="L4" s="41" t="inlineStr">
         <is>
           <t>예상결과</t>
         </is>
       </c>
-      <c r="M4" s="70" t="inlineStr">
+      <c r="M4" s="41" t="inlineStr">
         <is>
           <t>변경구분</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="26.1" customHeight="1" s="48">
-      <c r="A5" s="71" t="n"/>
-      <c r="B5" s="71" t="n"/>
-      <c r="C5" s="71" t="n"/>
-      <c r="D5" s="71" t="n"/>
-      <c r="E5" s="71" t="n"/>
-      <c r="F5" s="71" t="n"/>
-      <c r="G5" s="71" t="n"/>
-      <c r="H5" s="71" t="n"/>
-      <c r="I5" s="71" t="n"/>
-      <c r="J5" s="71" t="n"/>
-      <c r="K5" s="71" t="n"/>
-      <c r="L5" s="71" t="n"/>
-      <c r="M5" s="71" t="n"/>
+    <row r="5" ht="26" customHeight="1" s="46">
+      <c r="A5" s="42" t="n"/>
+      <c r="B5" s="42" t="n"/>
+      <c r="C5" s="42" t="n"/>
+      <c r="D5" s="42" t="n"/>
+      <c r="E5" s="42" t="n"/>
+      <c r="F5" s="42" t="n"/>
+      <c r="G5" s="42" t="n"/>
+      <c r="H5" s="42" t="n"/>
+      <c r="I5" s="42" t="n"/>
+      <c r="J5" s="42" t="n"/>
+      <c r="K5" s="42" t="n"/>
+      <c r="L5" s="42" t="n"/>
+      <c r="M5" s="42" t="n"/>
     </row>
-    <row r="6" ht="78" customHeight="1" s="48">
-      <c r="A6" s="67" t="n">
+    <row r="6" ht="78" customHeight="1" s="46">
+      <c r="A6" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="67" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>ITS-PAR-01</t>
         </is>
       </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>일일 민원 모니터링 → 위험 인지 → 알림 대응</t>
         </is>
       </c>
-      <c r="D6" s="67" t="inlineStr">
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>서비스관리자,
 일반사용자</t>
         </is>
       </c>
-      <c r="E6" s="67" t="inlineStr">
+      <c r="E6" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-01</t>
         </is>
       </c>
-      <c r="F6" s="67" t="inlineStr">
+      <c r="F6" s="43" t="inlineStr">
         <is>
           <t>사용자 메뉴 접근권한 조회</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>PR-CMM-003-03</t>
         </is>
       </c>
-      <c r="H6" s="67" t="inlineStr">
+      <c r="H6" s="43" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>로그인 및 권한별 메뉴 표출</t>
         </is>
@@ -9278,7 +8908,7 @@
 - 인증 성공 후 권한 기준 좌측 메뉴 구성 및 미허용 메뉴 차단 확인</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -9288,40 +8918,40 @@
           <t>- 인증 성공 후 권한에 맞는 메뉴만 표출되고 미허용 메뉴는 접근 차단</t>
         </is>
       </c>
-      <c r="M6" s="67" t="inlineStr">
+      <c r="M6" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="78" customHeight="1" s="48">
-      <c r="A7" s="67" t="n">
+    <row r="7" ht="78" customHeight="1" s="46">
+      <c r="A7" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="68" t="n"/>
-      <c r="C7" s="68" t="n"/>
-      <c r="D7" s="68" t="n"/>
-      <c r="E7" s="67" t="inlineStr">
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-02</t>
         </is>
       </c>
-      <c r="F7" s="67" t="inlineStr">
+      <c r="F7" s="43" t="inlineStr">
         <is>
           <t>메인 대시보드 조회</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-001-01</t>
         </is>
       </c>
-      <c r="H7" s="67" t="inlineStr">
+      <c r="H7" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-001</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>대시보드 초기 로딩·조회단위 전환</t>
         </is>
@@ -9332,9 +8962,9 @@
 - [어제/주간/월간]·상세 필터 전환</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
@@ -9342,46 +8972,46 @@
           <t>- 최신 민원 데이터 기준 전 위젯 표출, 조회 단위·기간 기준 일괄 갱신</t>
         </is>
       </c>
-      <c r="M7" s="67" t="inlineStr">
+      <c r="M7" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="78" customHeight="1" s="48">
-      <c r="A8" s="35" t="n">
+    <row r="8" ht="78" customHeight="1" s="46">
+      <c r="A8" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="68" t="n"/>
-      <c r="C8" s="68" t="n"/>
-      <c r="D8" s="68" t="n"/>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-03</t>
         </is>
       </c>
-      <c r="F8" s="35" t="inlineStr">
+      <c r="F8" s="43" t="inlineStr">
         <is>
           <t>[화면] 대시보드</t>
         </is>
       </c>
-      <c r="G8" s="36" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-001-01</t>
         </is>
       </c>
-      <c r="H8" s="35" t="inlineStr">
+      <c r="H8" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-001</t>
         </is>
       </c>
-      <c r="I8" s="37" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>현재 민원상황을 한눈에 파악하고 세부 화면으로 이동
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>- Header(메뉴명/최근 갱신 일시)
 - 조회 필터 바(어제/주간/월간 탭·상세 필터)
@@ -9392,50 +9022,50 @@
 - 분석·보고서·AI 최근목록 바로가기</t>
         </is>
       </c>
-      <c r="K8" s="39" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L8" s="38" t="inlineStr">
+      <c r="L8" s="1" t="inlineStr">
         <is>
           <t>- 대시보드 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M8" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M8" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="78" customHeight="1" s="48">
-      <c r="A9" s="67" t="n">
+    <row r="9" ht="78" customHeight="1" s="46">
+      <c r="A9" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="68" t="n"/>
-      <c r="C9" s="68" t="n"/>
-      <c r="D9" s="68" t="n"/>
-      <c r="E9" s="67" t="inlineStr">
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-04</t>
         </is>
       </c>
-      <c r="F9" s="67" t="inlineStr">
+      <c r="F9" s="43" t="inlineStr">
         <is>
           <t>민원현황 GIS 조회</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-002-01</t>
         </is>
       </c>
-      <c r="H9" s="67" t="inlineStr">
+      <c r="H9" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>GIS 히트맵·레이어·경계 조회</t>
         </is>
@@ -9448,9 +9078,9 @@
 - 공영주차장·행정동 경계 토글</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
@@ -9458,40 +9088,40 @@
           <t>- 조건 승계 후 선택 레이어 표시 전환, 히트맵 전환 시 그라데이션 범례, 마커·경계 표시/숨김 정상</t>
         </is>
       </c>
-      <c r="M9" s="67" t="inlineStr">
+      <c r="M9" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="78" customHeight="1" s="48">
-      <c r="A10" s="67" t="n">
+    <row r="10" ht="78" customHeight="1" s="46">
+      <c r="A10" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="68" t="n"/>
-      <c r="C10" s="68" t="n"/>
-      <c r="D10" s="68" t="n"/>
-      <c r="E10" s="67" t="inlineStr">
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-05</t>
         </is>
       </c>
-      <c r="F10" s="67" t="inlineStr">
+      <c r="F10" s="43" t="inlineStr">
         <is>
           <t>민원 상세 조회</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-002-02</t>
         </is>
       </c>
-      <c r="H10" s="67" t="inlineStr">
+      <c r="H10" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>지도 마커 상세 팝업</t>
         </is>
@@ -9501,9 +9131,9 @@
           <t>- 지도상 민원 마커 클릭</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr">
@@ -9511,40 +9141,40 @@
           <t>- 민원 구분·유형·건수 등 상세 팝업이 표출</t>
         </is>
       </c>
-      <c r="M10" s="67" t="inlineStr">
+      <c r="M10" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="78" customHeight="1" s="48">
-      <c r="A11" s="67" t="n">
+    <row r="11" ht="78" customHeight="1" s="46">
+      <c r="A11" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="68" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="68" t="n"/>
-      <c r="E11" s="67" t="inlineStr">
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-06</t>
         </is>
       </c>
-      <c r="F11" s="67" t="inlineStr">
+      <c r="F11" s="43" t="inlineStr">
         <is>
           <t>민원 검색</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-002-03</t>
         </is>
       </c>
-      <c r="H11" s="67" t="inlineStr">
+      <c r="H11" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>행정구역·유형·기간 검색</t>
         </is>
@@ -9554,9 +9184,9 @@
           <t>- 행정구역/민원유형/기간 필터 지정 후 검색</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
@@ -9564,46 +9194,46 @@
           <t>- 조건에 맞는 지역별 민원현황·집중구역 순위가 동시 갱신</t>
         </is>
       </c>
-      <c r="M11" s="67" t="inlineStr">
+      <c r="M11" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="78" customHeight="1" s="48">
-      <c r="A12" s="35" t="n">
+    <row r="12" ht="104" customHeight="1" s="46">
+      <c r="A12" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="68" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="68" t="n"/>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-07</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="43" t="inlineStr">
         <is>
           <t>[화면] 민원현황</t>
         </is>
       </c>
-      <c r="G12" s="36" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-002-01~03</t>
         </is>
       </c>
-      <c r="H12" s="35" t="inlineStr">
+      <c r="H12" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="I12" s="37" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>GIS 지도 기반 민원 현황 화면
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J12" s="38" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>- KPI 카드(총 민원건수/감정분석/단속집중지역/수요부족지역)
 - 레이어 설정(민원다발/집중단속/수요부족 중 택1, 민원 다발·단속 집중은 읍면동↔히트맵 전환)
@@ -9613,50 +9243,50 @@
 - 부정 민원 상위지역·구성비 막대차트</t>
         </is>
       </c>
-      <c r="K12" s="39" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L12" s="38" t="inlineStr">
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>- 민원현황 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M12" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M12" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="78" customHeight="1" s="48">
-      <c r="A13" s="67" t="n">
+    <row r="13" ht="78" customHeight="1" s="46">
+      <c r="A13" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="68" t="n"/>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="68" t="n"/>
-      <c r="E13" s="67" t="inlineStr">
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-08</t>
         </is>
       </c>
-      <c r="F13" s="67" t="inlineStr">
+      <c r="F13" s="43" t="inlineStr">
         <is>
           <t>위험단계 알림기준 관리</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-009-01</t>
         </is>
       </c>
-      <c r="H13" s="67" t="inlineStr">
+      <c r="H13" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-04</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>알림 기준·수신자 설정</t>
         </is>
@@ -9667,7 +9297,7 @@
 - 수신자 추가·활성화 토글</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>서비스관리자 권한 계정</t>
         </is>
@@ -9677,95 +9307,95 @@
           <t>- 기준이 저장·유지되고 활성화 여부에 따라 발송 대상 결정</t>
         </is>
       </c>
-      <c r="M13" s="67" t="inlineStr">
+      <c r="M13" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="78" customHeight="1" s="48">
-      <c r="A14" s="35" t="n">
+    <row r="14" ht="78" customHeight="1" s="46">
+      <c r="A14" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="68" t="n"/>
-      <c r="E14" s="35" t="inlineStr">
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-09</t>
         </is>
       </c>
-      <c r="F14" s="35" t="inlineStr">
+      <c r="F14" s="43" t="inlineStr">
         <is>
           <t>[화면] 위험단계 알림 관리</t>
         </is>
       </c>
-      <c r="G14" s="36" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-009-01</t>
         </is>
       </c>
-      <c r="H14" s="35" t="inlineStr">
+      <c r="H14" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-04</t>
         </is>
       </c>
-      <c r="I14" s="37" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>위험단계 알림 수신자·기준 관리(관리자 전용)
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J14" s="38" t="inlineStr">
+      <c r="J14" s="1" t="inlineStr">
         <is>
           <t>- 수신자 관리(위험 수신자 등록·관리)
 - 알림 기준 설정(심각/경고/주의 % 입력·설정 저장)</t>
         </is>
       </c>
-      <c r="K14" s="39" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>서비스관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L14" s="38" t="inlineStr">
+      <c r="L14" s="1" t="inlineStr">
         <is>
           <t>- 위험단계 알림 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M14" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M14" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="78" customHeight="1" s="48">
-      <c r="A15" s="67" t="n">
+    <row r="15" ht="78" customHeight="1" s="46">
+      <c r="A15" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="68" t="n"/>
-      <c r="C15" s="68" t="n"/>
-      <c r="D15" s="68" t="n"/>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-10</t>
         </is>
       </c>
-      <c r="F15" s="67" t="inlineStr">
+      <c r="F15" s="43" t="inlineStr">
         <is>
           <t>위험단계 알림이력 조회</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-009-02</t>
         </is>
       </c>
-      <c r="H15" s="67" t="inlineStr">
+      <c r="H15" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-03</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>알림 이력 조회</t>
         </is>
@@ -9775,9 +9405,9 @@
           <t>- 단계/지역/기간 필터 적용</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
@@ -9785,109 +9415,109 @@
           <t>- 조건에 맞는 알림 이력이 단계 뱃지와 함께 목록 표출</t>
         </is>
       </c>
-      <c r="M15" s="67" t="inlineStr">
+      <c r="M15" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="78" customHeight="1" s="48">
-      <c r="A16" s="35" t="n">
+    <row r="16" ht="78" customHeight="1" s="46">
+      <c r="A16" s="43" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="69" t="n"/>
-      <c r="C16" s="69" t="n"/>
-      <c r="D16" s="69" t="n"/>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="B16" s="45" t="n"/>
+      <c r="C16" s="45" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-01-11</t>
         </is>
       </c>
-      <c r="F16" s="35" t="inlineStr">
+      <c r="F16" s="43" t="inlineStr">
         <is>
           <t>[화면] 위험단계 알림 조회</t>
         </is>
       </c>
-      <c r="G16" s="36" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-009-02</t>
         </is>
       </c>
-      <c r="H16" s="35" t="inlineStr">
+      <c r="H16" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-03</t>
         </is>
       </c>
-      <c r="I16" s="37" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>위험단계 알림 이력 조회
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J16" s="38" t="inlineStr">
+      <c r="J16" s="1" t="inlineStr">
         <is>
           <t>- KPI 카드(총 민원건수/위험알림 건수/미처리 알림 건수)
 - 조회 필터(단계/지역/기간)
 - 알림 이력(단계/지역/내용/일시/민원 수/처리상태)</t>
         </is>
       </c>
-      <c r="K16" s="39" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L16" s="38" t="inlineStr">
+      <c r="L16" s="1" t="inlineStr">
         <is>
           <t>- 위험단계 알림 조회 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M16" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M16" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="78" customHeight="1" s="48">
-      <c r="A17" s="67" t="n">
+    <row r="17" ht="78" customHeight="1" s="46">
+      <c r="A17" s="43" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="67" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>ITS-PAR-02</t>
         </is>
       </c>
-      <c r="C17" s="67" t="inlineStr">
+      <c r="C17" s="43" t="inlineStr">
         <is>
           <t>집중구역 진단 → 정책 효과 시뮬레이션 → 보고서</t>
         </is>
       </c>
-      <c r="D17" s="67" t="inlineStr">
+      <c r="D17" s="43" t="inlineStr">
         <is>
           <t>서비스관리자,
 일반사용자</t>
         </is>
       </c>
-      <c r="E17" s="67" t="inlineStr">
+      <c r="E17" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-02-01</t>
         </is>
       </c>
-      <c r="F17" s="67" t="inlineStr">
+      <c r="F17" s="43" t="inlineStr">
         <is>
           <t>집중구역 분석 실행</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-003-01</t>
         </is>
       </c>
-      <c r="H17" s="67" t="inlineStr">
+      <c r="H17" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-01</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>집중구역 자동 도출</t>
         </is>
@@ -9897,9 +9527,9 @@
           <t>- 분석 지역(제주시)·기간(최근3개월) 설정 후 [분석 실행]</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -9907,40 +9537,40 @@
           <t>- 종합점수 기준 집중구역 자동 도출, 지도·순위 갱신</t>
         </is>
       </c>
-      <c r="M17" s="67" t="inlineStr">
+      <c r="M17" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="78" customHeight="1" s="48">
-      <c r="A18" s="67" t="n">
+    <row r="18" ht="78" customHeight="1" s="46">
+      <c r="A18" s="43" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="68" t="n"/>
-      <c r="C18" s="68" t="n"/>
-      <c r="D18" s="68" t="n"/>
-      <c r="E18" s="67" t="inlineStr">
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-02-02</t>
         </is>
       </c>
-      <c r="F18" s="67" t="inlineStr">
+      <c r="F18" s="43" t="inlineStr">
         <is>
           <t>집중구역 순위 조회</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-003-02</t>
         </is>
       </c>
-      <c r="H18" s="67" t="inlineStr">
+      <c r="H18" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-01</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>지도 마커·순위표</t>
         </is>
@@ -9950,9 +9580,9 @@
           <t>- 지도 마커 클릭 및 우측 순위표 확인</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -9960,96 +9590,96 @@
           <t>- 순위·구역명·민원/단속 건수 팝업 및 순위 리스트 표출</t>
         </is>
       </c>
-      <c r="M18" s="67" t="inlineStr">
+      <c r="M18" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="78" customHeight="1" s="48">
-      <c r="A19" s="35" t="n">
+    <row r="19" ht="78" customHeight="1" s="46">
+      <c r="A19" s="43" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="68" t="n"/>
-      <c r="C19" s="68" t="n"/>
-      <c r="D19" s="68" t="n"/>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-02-03</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="F19" s="43" t="inlineStr">
         <is>
           <t>[화면] 불법 주차 불법 주차 집중 구역 분석</t>
         </is>
       </c>
-      <c r="G19" s="36" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-003-01~02</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr">
+      <c r="H19" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-01</t>
         </is>
       </c>
-      <c r="I19" s="37" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>불법주차 집중 구역 자동 도출
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J19" s="38" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>- 분석 설정(지역 드롭다운·기간 탭/날짜 피커·분석 실행)
 - 지도 시각화(집중구역 마커/순위·클릭 팝업)
 - 종합점수 기준(민원·단속 건수 가중합) 구역 순위(구역명/민원/단속 건수)</t>
         </is>
       </c>
-      <c r="K19" s="39" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L19" s="38" t="inlineStr">
+      <c r="L19" s="1" t="inlineStr">
         <is>
           <t>- 불법 주차 불법 주차 집중 구역 분석 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M19" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M19" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="78" customHeight="1" s="48">
-      <c r="A20" s="67" t="n">
+    <row r="20" ht="78" customHeight="1" s="46">
+      <c r="A20" s="43" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="68" t="n"/>
-      <c r="C20" s="68" t="n"/>
-      <c r="D20" s="68" t="n"/>
-      <c r="E20" s="67" t="inlineStr">
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-02-04</t>
         </is>
       </c>
-      <c r="F20" s="67" t="inlineStr">
+      <c r="F20" s="43" t="inlineStr">
         <is>
           <t>정책시뮬레이션 실행</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-004-01</t>
         </is>
       </c>
-      <c r="H20" s="67" t="inlineStr">
+      <c r="H20" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-02</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>정책 효과 예측</t>
         </is>
@@ -10059,9 +9689,9 @@
           <t>- 정책 유형(주차장 확충/이면도로/요금제)·변수 입력 후 [시뮬레이션 실행]</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>차량관리과 담당자 권한 계정</t>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr">
@@ -10069,40 +9699,40 @@
           <t>- 정책별 효과 예측 차트·민원 감소·혼잡도 개선 수치 산출</t>
         </is>
       </c>
-      <c r="M20" s="67" t="inlineStr">
+      <c r="M20" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="78" customHeight="1" s="48">
-      <c r="A21" s="67" t="n">
+    <row r="21" ht="78" customHeight="1" s="46">
+      <c r="A21" s="43" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="68" t="n"/>
-      <c r="C21" s="68" t="n"/>
-      <c r="D21" s="68" t="n"/>
-      <c r="E21" s="67" t="inlineStr">
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-02-05</t>
         </is>
       </c>
-      <c r="F21" s="67" t="inlineStr">
+      <c r="F21" s="43" t="inlineStr">
         <is>
           <t>시뮬레이션 결과 비교</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-004-02</t>
         </is>
       </c>
-      <c r="H21" s="67" t="inlineStr">
+      <c r="H21" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-02</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>시나리오 비교</t>
         </is>
@@ -10112,9 +9742,9 @@
           <t>- 하단 시나리오 비교 테이블 확인</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>차량관리과 담당자 권한 계정</t>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -10122,46 +9752,46 @@
           <t>- 시나리오별 감소율·개선·비용 비교 및 추천 배지 부여</t>
         </is>
       </c>
-      <c r="M21" s="67" t="inlineStr">
+      <c r="M21" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="78" customHeight="1" s="48">
-      <c r="A22" s="35" t="n">
+    <row r="22" ht="78" customHeight="1" s="46">
+      <c r="A22" s="43" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="68" t="n"/>
-      <c r="C22" s="68" t="n"/>
-      <c r="D22" s="68" t="n"/>
-      <c r="E22" s="35" t="inlineStr">
+      <c r="B22" s="44" t="n"/>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-02-06</t>
         </is>
       </c>
-      <c r="F22" s="35" t="inlineStr">
+      <c r="F22" s="43" t="inlineStr">
         <is>
           <t>[화면] 정책 효과 시뮬레이션</t>
         </is>
       </c>
-      <c r="G22" s="36" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-004-01~02</t>
         </is>
       </c>
-      <c r="H22" s="35" t="inlineStr">
+      <c r="H22" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-02</t>
         </is>
       </c>
-      <c r="I22" s="37" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>정책 변수 입력→효과 예측→시나리오 비교
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J22" s="38" t="inlineStr">
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>- 정책변수설정(주차장확충/이면도로/요금제·지역·예측기간·증설수·실행)
 - 효과예측 패널(민원감소/혼잡도개선 라인차트)
@@ -10169,101 +9799,101 @@
 - 비교결과 PDF 리포트 자동생성</t>
         </is>
       </c>
-      <c r="K22" s="39" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L22" s="38" t="inlineStr">
+      <c r="L22" s="1" t="inlineStr">
         <is>
           <t>- 정책 효과 시뮬레이션 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M22" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M22" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="78" customHeight="1" s="48">
-      <c r="A23" s="35" t="n">
+    <row r="23" ht="78" customHeight="1" s="46">
+      <c r="A23" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="68" t="n"/>
-      <c r="C23" s="68" t="n"/>
-      <c r="D23" s="68" t="n"/>
-      <c r="E23" s="35" t="inlineStr">
+      <c r="B23" s="44" t="n"/>
+      <c r="C23" s="44" t="n"/>
+      <c r="D23" s="44" t="n"/>
+      <c r="E23" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-02-07</t>
         </is>
       </c>
-      <c r="F23" s="35" t="inlineStr">
+      <c r="F23" s="43" t="inlineStr">
         <is>
           <t>[화면] 정책 효과 시뮬레이션(상세)</t>
         </is>
       </c>
-      <c r="G23" s="36" t="n"/>
-      <c r="H23" s="35" t="inlineStr">
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-02-1</t>
         </is>
       </c>
-      <c r="I23" s="37" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>정책변수설정 상세(이면도로/요금제)
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J23" s="38" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>- 정책변수설정(이면도로 정비: 지역·기간·정비유형·실행)
 - 정책변수설정(요금제 적용: 지역·기간·요금 급지·실행)</t>
         </is>
       </c>
-      <c r="K23" s="39" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L23" s="38" t="inlineStr">
+      <c r="L23" s="1" t="inlineStr">
         <is>
           <t>- 정책 시뮬레이션(상세) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M23" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M23" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="78" customHeight="1" s="48">
-      <c r="A24" s="67" t="n">
+    <row r="24" ht="78" customHeight="1" s="46">
+      <c r="A24" s="43" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="69" t="n"/>
-      <c r="C24" s="69" t="n"/>
-      <c r="D24" s="69" t="n"/>
-      <c r="E24" s="67" t="inlineStr">
+      <c r="B24" s="45" t="n"/>
+      <c r="C24" s="45" t="n"/>
+      <c r="D24" s="45" t="n"/>
+      <c r="E24" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-02-08</t>
         </is>
       </c>
-      <c r="F24" s="67" t="inlineStr">
+      <c r="F24" s="43" t="inlineStr">
         <is>
           <t>보고서 목록 조회(내보내기)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-008-01</t>
         </is>
       </c>
-      <c r="H24" s="67" t="inlineStr">
+      <c r="H24" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-01</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>분석·시뮬 결과 보고서 내보내기</t>
         </is>
@@ -10273,9 +9903,9 @@
           <t>- [내보내기] 후 보고서 관리 진입</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>차량관리과 담당자 권한 계정</t>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr">
@@ -10283,53 +9913,53 @@
           <t>- 직접 생성 보고서 목록에 등록되고 미리보기·PDF 다운로드 동작</t>
         </is>
       </c>
-      <c r="M24" s="67" t="inlineStr">
+      <c r="M24" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="78" customHeight="1" s="48">
-      <c r="A25" s="67" t="n">
+    <row r="25" ht="78" customHeight="1" s="46">
+      <c r="A25" s="43" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="67" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>ITS-PAR-03</t>
         </is>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>생활권 수급 분석 → 요금제·공유주차제 구역 선정</t>
         </is>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="43" t="inlineStr">
         <is>
           <t>서비스관리자,
 일반사용자</t>
         </is>
       </c>
-      <c r="E25" s="67" t="inlineStr">
+      <c r="E25" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-03-01</t>
         </is>
       </c>
-      <c r="F25" s="67" t="inlineStr">
+      <c r="F25" s="43" t="inlineStr">
         <is>
           <t>생활권 격자분석 실행</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-005-01</t>
         </is>
       </c>
-      <c r="H25" s="67" t="inlineStr">
+      <c r="H25" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-03</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>격자 기반 수급 분석</t>
         </is>
@@ -10340,9 +9970,9 @@
 - 격자 클릭 상세 확인</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>차량관리과 담당자 권한 계정</t>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
@@ -10350,46 +9980,46 @@
           <t>- 제주 전역 격자 히트맵 표출, 위험단계·건수 팝업 및 집중구역 요약</t>
         </is>
       </c>
-      <c r="M25" s="67" t="inlineStr">
+      <c r="M25" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="78" customHeight="1" s="48">
-      <c r="A26" s="35" t="n">
+    <row r="26" ht="78" customHeight="1" s="46">
+      <c r="A26" s="43" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="68" t="n"/>
-      <c r="C26" s="68" t="n"/>
-      <c r="D26" s="68" t="n"/>
-      <c r="E26" s="35" t="inlineStr">
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-03-02</t>
         </is>
       </c>
-      <c r="F26" s="35" t="inlineStr">
+      <c r="F26" s="43" t="inlineStr">
         <is>
           <t>[화면] 생활권 시뮬레이션</t>
         </is>
       </c>
-      <c r="G26" s="36" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-005-01</t>
         </is>
       </c>
-      <c r="H26" s="35" t="inlineStr">
+      <c r="H26" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-03</t>
         </is>
       </c>
-      <c r="I26" s="37" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>격자(Grid) 기반 민원·수급·혼잡도 공간 분석
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J26" s="38" t="inlineStr">
+      <c r="J26" s="1" t="inlineStr">
         <is>
           <t>- 분석 설정(내용: 민원/수급/혼잡도·지역·기간·격자 100~500m·실행)
 - GIS 격자 히트맵·클릭 상세 팝업·범례
@@ -10397,50 +10027,50 @@
 - 민원집중구역(동+격자 POI 명칭)</t>
         </is>
       </c>
-      <c r="K26" s="39" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L26" s="38" t="inlineStr">
+      <c r="L26" s="1" t="inlineStr">
         <is>
           <t>- 생활권 시뮬레이션 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M26" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M26" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="78" customHeight="1" s="48">
-      <c r="A27" s="67" t="n">
+    <row r="27" ht="78" customHeight="1" s="46">
+      <c r="A27" s="43" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="68" t="n"/>
-      <c r="C27" s="68" t="n"/>
-      <c r="D27" s="68" t="n"/>
-      <c r="E27" s="67" t="inlineStr">
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-03-03</t>
         </is>
       </c>
-      <c r="F27" s="67" t="inlineStr">
+      <c r="F27" s="43" t="inlineStr">
         <is>
           <t>요금제·공유주차 구역추천</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-006-01</t>
         </is>
       </c>
-      <c r="H27" s="67" t="inlineStr">
+      <c r="H27" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-04</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>구역 추천 실행·순위</t>
         </is>
@@ -10451,9 +10081,9 @@
 - 추천 마커·순위·산정 기준 안내(ⓘ) 확인</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>차량관리과 담당자 권한 계정</t>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
@@ -10461,96 +10091,96 @@
           <t>- 민원 증가 추세를 반영한 추천 구역이 자동 도출되고 우선순위 마커·순위 표출</t>
         </is>
       </c>
-      <c r="M27" s="67" t="inlineStr">
+      <c r="M27" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="78" customHeight="1" s="48">
-      <c r="A28" s="35" t="n">
+    <row r="28" ht="78" customHeight="1" s="46">
+      <c r="A28" s="43" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="68" t="n"/>
-      <c r="C28" s="68" t="n"/>
-      <c r="D28" s="68" t="n"/>
-      <c r="E28" s="35" t="inlineStr">
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-03-04</t>
         </is>
       </c>
-      <c r="F28" s="35" t="inlineStr">
+      <c r="F28" s="43" t="inlineStr">
         <is>
           <t>[화면] 구역추천</t>
         </is>
       </c>
-      <c r="G28" s="36" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-006-01</t>
         </is>
       </c>
-      <c r="H28" s="35" t="inlineStr">
+      <c r="H28" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-04</t>
         </is>
       </c>
-      <c r="I28" s="37" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>민원 증가 추세 기반 요금제·공유주차제 최적 구역 추천
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J28" s="38" t="inlineStr">
+      <c r="J28" s="1" t="inlineStr">
         <is>
           <t>- 추천 설정(요금제/공유주차제·지역·분석 기간·실행)
 - 지도 추천 핀(우선순위 범례)·클릭 팝업
 - 추천 구역 순위(산정 기준 ⓘ·목록-지도 연동)</t>
         </is>
       </c>
-      <c r="K28" s="39" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L28" s="38" t="inlineStr">
+      <c r="L28" s="1" t="inlineStr">
         <is>
           <t>- 구역추천 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M28" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M28" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="78" customHeight="1" s="48">
-      <c r="A29" s="67" t="n">
+    <row r="29" ht="78" customHeight="1" s="46">
+      <c r="A29" s="43" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="69" t="n"/>
-      <c r="C29" s="69" t="n"/>
-      <c r="D29" s="69" t="n"/>
-      <c r="E29" s="67" t="inlineStr">
+      <c r="B29" s="45" t="n"/>
+      <c r="C29" s="45" t="n"/>
+      <c r="D29" s="45" t="n"/>
+      <c r="E29" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-03-05</t>
         </is>
       </c>
-      <c r="F29" s="67" t="inlineStr">
+      <c r="F29" s="43" t="inlineStr">
         <is>
           <t>보고서 목록 조회(내보내기)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-008-01</t>
         </is>
       </c>
-      <c r="H29" s="67" t="inlineStr">
+      <c r="H29" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-01</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>구역 선정 보고서 내보내기</t>
         </is>
@@ -10560,9 +10190,9 @@
           <t>- [내보내기] 후 보고서 관리 진입</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>차량관리과 담당자 권한 계정</t>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
@@ -10570,53 +10200,53 @@
           <t>- 보고서 목록 등록 및 미리보기·다운로드 동작</t>
         </is>
       </c>
-      <c r="M29" s="67" t="inlineStr">
+      <c r="M29" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="78" customHeight="1" s="48">
-      <c r="A30" s="67" t="n">
+    <row r="30" ht="78" customHeight="1" s="46">
+      <c r="A30" s="43" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="67" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>ITS-PAR-04</t>
         </is>
       </c>
-      <c r="C30" s="67" t="inlineStr">
+      <c r="C30" s="43" t="inlineStr">
         <is>
           <t>투자·보강 우선순위 산정 → 보고서</t>
         </is>
       </c>
-      <c r="D30" s="67" t="inlineStr">
+      <c r="D30" s="43" t="inlineStr">
         <is>
           <t>서비스관리자,
 일반사용자</t>
         </is>
       </c>
-      <c r="E30" s="67" t="inlineStr">
+      <c r="E30" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-04-01</t>
         </is>
       </c>
-      <c r="F30" s="67" t="inlineStr">
+      <c r="F30" s="43" t="inlineStr">
         <is>
           <t>투자우선순위 분석</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-007-01</t>
         </is>
       </c>
-      <c r="H30" s="67" t="inlineStr">
+      <c r="H30" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-05</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>종합 지표 기반 우선순위 산정</t>
         </is>
@@ -10627,9 +10257,9 @@
 - 마커/요약 카드/순위 리스트 확인</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>차량관리과 담당자 권한 계정</t>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr">
@@ -10637,96 +10267,96 @@
           <t>- 안전위험도·민원빈도·이용패턴·사고이력 가중치 종합점수 자동 산정, 요약·순위 정합</t>
         </is>
       </c>
-      <c r="M30" s="67" t="inlineStr">
+      <c r="M30" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="78" customHeight="1" s="48">
-      <c r="A31" s="35" t="n">
+    <row r="31" ht="78" customHeight="1" s="46">
+      <c r="A31" s="43" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="68" t="n"/>
-      <c r="C31" s="68" t="n"/>
-      <c r="D31" s="68" t="n"/>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="B31" s="44" t="n"/>
+      <c r="C31" s="44" t="n"/>
+      <c r="D31" s="44" t="n"/>
+      <c r="E31" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-04-02</t>
         </is>
       </c>
-      <c r="F31" s="35" t="inlineStr">
+      <c r="F31" s="43" t="inlineStr">
         <is>
           <t>[화면] 투자우선순위 보드</t>
         </is>
       </c>
-      <c r="G31" s="36" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-007-01</t>
         </is>
       </c>
-      <c r="H31" s="35" t="inlineStr">
+      <c r="H31" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003-05</t>
         </is>
       </c>
-      <c r="I31" s="37" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>안전위험·민원·이용·사고 종합지표로 투자·보강 우선순위 산정
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J31" s="38" t="inlineStr">
+      <c r="J31" s="1" t="inlineStr">
         <is>
           <t>- 요약 카드(대상 주차장 수/높음 개소/최근3개월 사고)
 - 지도 P핀 마커(우선순위 컬러·순위)·클릭 4지표 팝업
 - 종합점수(안전위험도·민원빈도·이용패턴·사고이력) 순위 배지</t>
         </is>
       </c>
-      <c r="K31" s="39" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L31" s="38" t="inlineStr">
+      <c r="L31" s="1" t="inlineStr">
         <is>
           <t>- 투자우선순위 보드 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M31" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M31" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="78" customHeight="1" s="48">
-      <c r="A32" s="67" t="n">
+    <row r="32" ht="78" customHeight="1" s="46">
+      <c r="A32" s="43" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="69" t="n"/>
-      <c r="C32" s="69" t="n"/>
-      <c r="D32" s="69" t="n"/>
-      <c r="E32" s="67" t="inlineStr">
+      <c r="B32" s="45" t="n"/>
+      <c r="C32" s="45" t="n"/>
+      <c r="D32" s="45" t="n"/>
+      <c r="E32" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-04-03</t>
         </is>
       </c>
-      <c r="F32" s="67" t="inlineStr">
+      <c r="F32" s="43" t="inlineStr">
         <is>
           <t>보고서 목록 조회(내보내기)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-008-01</t>
         </is>
       </c>
-      <c r="H32" s="67" t="inlineStr">
+      <c r="H32" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-01</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>투자우선순위 보고서 내보내기</t>
         </is>
@@ -10736,9 +10366,9 @@
           <t>- [내보내기] 후 보고서 관리 진입</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>차량관리과 담당자 권한 계정</t>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr">
@@ -10746,37 +10376,37 @@
           <t>- 보고서 목록 등록 및 다운로드 동작</t>
         </is>
       </c>
-      <c r="M32" s="67" t="inlineStr">
+      <c r="M32" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="78" customHeight="1" s="48">
-      <c r="A33" s="67" t="n">
+    <row r="33" ht="78" customHeight="1" s="46">
+      <c r="A33" s="43" t="n">
         <v>28</v>
       </c>
-      <c r="E33" s="67" t="inlineStr">
+      <c r="E33" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-05-01</t>
         </is>
       </c>
-      <c r="F33" s="67" t="inlineStr">
+      <c r="F33" s="43" t="inlineStr">
         <is>
           <t>AI 대화 세션 관리</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-010-01</t>
         </is>
       </c>
-      <c r="H33" s="67" t="inlineStr">
+      <c r="H33" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>자연어 질의(sLLM+RAG)</t>
         </is>
@@ -10787,9 +10417,9 @@
 - sLLM 응답 및 세션 이력 확인</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr">
@@ -10797,37 +10427,37 @@
           <t>- sLLM 자연어 응답이 정상 표출되고 대화 세션·메시지가 관리됨</t>
         </is>
       </c>
-      <c r="M33" s="67" t="inlineStr">
+      <c r="M33" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="78" customHeight="1" s="48">
-      <c r="A34" s="67" t="n">
+    <row r="34" ht="78" customHeight="1" s="46">
+      <c r="A34" s="43" t="n">
         <v>29</v>
       </c>
-      <c r="E34" s="67" t="inlineStr">
+      <c r="E34" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-05-02</t>
         </is>
       </c>
-      <c r="F34" s="67" t="inlineStr">
+      <c r="F34" s="43" t="inlineStr">
         <is>
           <t>조례 인용·문서 조회</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-010-02</t>
         </is>
       </c>
-      <c r="H34" s="67" t="inlineStr">
+      <c r="H34" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>RAG 조례 인용 카드</t>
         </is>
@@ -10838,9 +10468,9 @@
 - 조례명·관련 조문 발췌 응답 확인</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr">
@@ -10848,43 +10478,43 @@
           <t>- 관련 조례가 조례명·조문 발췌로 표출되고 답변에 반영</t>
         </is>
       </c>
-      <c r="M34" s="67" t="inlineStr">
+      <c r="M34" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="78" customHeight="1" s="48">
-      <c r="A35" s="35" t="n">
+    <row r="35" ht="78" customHeight="1" s="46">
+      <c r="A35" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="E35" s="35" t="inlineStr">
+      <c r="E35" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-05-03</t>
         </is>
       </c>
-      <c r="F35" s="35" t="inlineStr">
+      <c r="F35" s="43" t="inlineStr">
         <is>
           <t>[화면] AI 어시스턴트(행정조례검색)</t>
         </is>
       </c>
-      <c r="G35" s="36" t="inlineStr">
+      <c r="G35" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-010-01~04</t>
         </is>
       </c>
-      <c r="H35" s="35" t="inlineStr">
+      <c r="H35" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="I35" s="37" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>sLLM+RAG 기반 대화형 행정 정보 검색
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J35" s="38" t="inlineStr">
+      <c r="J35" s="1" t="inlineStr">
         <is>
           <t>- 채팅 영역(조례 인용: 조례명+관련 조문 발췌)
 - sLLM·RAG 정책문서·조례 검색
@@ -10892,47 +10522,47 @@
 - 최근 대화·최근 리포트</t>
         </is>
       </c>
-      <c r="K35" s="39" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L35" s="38" t="inlineStr">
+      <c r="L35" s="1" t="inlineStr">
         <is>
           <t>- AI 어시스턴트(행정조례검색) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M35" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M35" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="78" customHeight="1" s="48">
-      <c r="A36" s="67" t="n">
+    <row r="36" ht="78" customHeight="1" s="46">
+      <c r="A36" s="43" t="n">
         <v>31</v>
       </c>
-      <c r="E36" s="67" t="inlineStr">
+      <c r="E36" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-05-04</t>
         </is>
       </c>
-      <c r="F36" s="67" t="inlineStr">
+      <c r="F36" s="43" t="inlineStr">
         <is>
           <t>대량 민원 자동 요약</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-010-01</t>
         </is>
       </c>
-      <c r="H36" s="67" t="inlineStr">
+      <c r="H36" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-005-02</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>AI 대량 민원 내용 요약</t>
         </is>
@@ -10943,9 +10573,9 @@
 - AI 응답의 요약 결과 및 [리포트 생성] 확인</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr">
@@ -10953,85 +10583,85 @@
           <t>- 대량 민원 내용이 요약되어 표출되고 리포트 생성 버튼 제공</t>
         </is>
       </c>
-      <c r="M36" s="67" t="inlineStr">
+      <c r="M36" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="78" customHeight="1" s="48">
-      <c r="A37" s="35" t="n">
+    <row r="37" ht="78" customHeight="1" s="46">
+      <c r="A37" s="43" t="n">
         <v>32</v>
       </c>
-      <c r="E37" s="35" t="inlineStr">
+      <c r="E37" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-05-05</t>
         </is>
       </c>
-      <c r="F37" s="35" t="inlineStr">
+      <c r="F37" s="43" t="inlineStr">
         <is>
           <t>[화면] AI 어시스턴트(대량 민원 자동 요약)</t>
         </is>
       </c>
-      <c r="G37" s="36" t="n"/>
-      <c r="H37" s="35" t="inlineStr">
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-005-02</t>
         </is>
       </c>
-      <c r="I37" s="37" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>sLLM+RAG 기반 대량 민원 내용 자동 요약
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J37" s="38" t="inlineStr">
+      <c r="J37" s="1" t="inlineStr">
         <is>
           <t>- 채팅 영역
 - AI 응답 시 대량 민원 내용 요약(리포트 생성 버튼 제공)</t>
         </is>
       </c>
-      <c r="K37" s="39" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L37" s="38" t="inlineStr">
+      <c r="L37" s="1" t="inlineStr">
         <is>
           <t>- AI 어시스턴트(대량 민원 자동 요약) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M37" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M37" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="78" customHeight="1" s="48">
-      <c r="A38" s="67" t="n">
+    <row r="38" ht="78" customHeight="1" s="46">
+      <c r="A38" s="43" t="n">
         <v>33</v>
       </c>
-      <c r="E38" s="67" t="inlineStr">
+      <c r="E38" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-05-06</t>
         </is>
       </c>
-      <c r="F38" s="67" t="inlineStr">
+      <c r="F38" s="43" t="inlineStr">
         <is>
           <t>요약 보고서 미리보기·다운로드</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-010-01</t>
         </is>
       </c>
-      <c r="H38" s="67" t="inlineStr">
+      <c r="H38" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-005-03</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>민원요약 보고서 출력</t>
         </is>
@@ -11042,9 +10672,9 @@
 - PDF/DOCX 다운로드</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L38" s="1" t="inlineStr">
@@ -11052,101 +10682,101 @@
           <t>- 민원요약 보고서 미리보기 표출 및 PDF·DOCX 다운로드</t>
         </is>
       </c>
-      <c r="M38" s="67" t="inlineStr">
+      <c r="M38" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="78" customHeight="1" s="48">
-      <c r="A39" s="35" t="n">
+    <row r="39" ht="78" customHeight="1" s="46">
+      <c r="A39" s="43" t="n">
         <v>34</v>
       </c>
-      <c r="E39" s="35" t="inlineStr">
+      <c r="E39" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-05-07</t>
         </is>
       </c>
-      <c r="F39" s="35" t="inlineStr">
+      <c r="F39" s="43" t="inlineStr">
         <is>
           <t>[화면] AI 어시스턴트(보고서 미리보기·다운로드)</t>
         </is>
       </c>
-      <c r="G39" s="36" t="n"/>
-      <c r="H39" s="35" t="inlineStr">
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-005-03</t>
         </is>
       </c>
-      <c r="I39" s="37" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>민원요약 보고서 미리보기·다운로드
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J39" s="38" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>- 민원요약 보고서 미리보기
 - 보고서 다운로드(PDF, DOCX)</t>
         </is>
       </c>
-      <c r="K39" s="39" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L39" s="38" t="inlineStr">
+      <c r="L39" s="1" t="inlineStr">
         <is>
           <t>- AI 어시스턴트(보고서 미리보기·다운로드) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M39" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M39" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="78" customHeight="1" s="48">
-      <c r="A40" s="67" t="n">
+    <row r="40" ht="78" customHeight="1" s="46">
+      <c r="A40" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="B40" s="67" t="inlineStr">
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>ITS-PAR-06</t>
         </is>
       </c>
-      <c r="C40" s="67" t="inlineStr">
+      <c r="C40" s="43" t="inlineStr">
         <is>
           <t>정기 보고서 자동 생성 설정 → 열람</t>
         </is>
       </c>
-      <c r="D40" s="67" t="inlineStr">
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t>서비스관리자,
 일반사용자</t>
         </is>
       </c>
-      <c r="E40" s="67" t="inlineStr">
+      <c r="E40" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-06-01</t>
         </is>
       </c>
-      <c r="F40" s="67" t="inlineStr">
+      <c r="F40" s="43" t="inlineStr">
         <is>
           <t>보고서 자동생성 설정</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-008-02</t>
         </is>
       </c>
-      <c r="H40" s="67" t="inlineStr">
+      <c r="H40" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-02</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>배포주기·배포일자 설정</t>
         </is>
@@ -11156,7 +10786,7 @@
           <t>- 배포 주기/일자 선택 후 [보고서 자동 생성]</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>서비스관리자 권한 계정</t>
         </is>
@@ -11166,95 +10796,95 @@
           <t>- 자동 생성 설정 저장 및 자동 생성 목록에 항목 추가</t>
         </is>
       </c>
-      <c r="M40" s="67" t="inlineStr">
+      <c r="M40" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="78" customHeight="1" s="48">
-      <c r="A41" s="35" t="n">
+    <row r="41" ht="78" customHeight="1" s="46">
+      <c r="A41" s="43" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="68" t="n"/>
-      <c r="C41" s="68" t="n"/>
-      <c r="D41" s="68" t="n"/>
-      <c r="E41" s="35" t="inlineStr">
+      <c r="B41" s="44" t="n"/>
+      <c r="C41" s="44" t="n"/>
+      <c r="D41" s="44" t="n"/>
+      <c r="E41" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-06-02</t>
         </is>
       </c>
-      <c r="F41" s="35" t="inlineStr">
+      <c r="F41" s="43" t="inlineStr">
         <is>
           <t>[화면] 보고서 관리</t>
         </is>
       </c>
-      <c r="G41" s="36" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-008-02</t>
         </is>
       </c>
-      <c r="H41" s="35" t="inlineStr">
+      <c r="H41" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-02</t>
         </is>
       </c>
-      <c r="I41" s="37" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>민원 분석 결과 보고서 자동 생성 관리(관리자 전용)
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J41" s="38" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>- 자동 생성 설정(배포부서/배포주기/배포일자 드롭다운·자동생성 버튼)
 - 자동 생성 설정 목록(조회·수정·삭제)</t>
         </is>
       </c>
-      <c r="K41" s="39" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>서비스관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L41" s="38" t="inlineStr">
+      <c r="L41" s="1" t="inlineStr">
         <is>
           <t>- 보고서 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M41" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M41" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="78" customHeight="1" s="48">
-      <c r="A42" s="67" t="n">
+    <row r="42" ht="78" customHeight="1" s="46">
+      <c r="A42" s="43" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="68" t="n"/>
-      <c r="C42" s="68" t="n"/>
-      <c r="D42" s="68" t="n"/>
-      <c r="E42" s="67" t="inlineStr">
+      <c r="B42" s="44" t="n"/>
+      <c r="C42" s="44" t="n"/>
+      <c r="D42" s="44" t="n"/>
+      <c r="E42" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-06-03</t>
         </is>
       </c>
-      <c r="F42" s="67" t="inlineStr">
+      <c r="F42" s="43" t="inlineStr">
         <is>
           <t>보고서 목록 조회·열람</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-008-01</t>
         </is>
       </c>
-      <c r="H42" s="67" t="inlineStr">
+      <c r="H42" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-01</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>미리보기·다운로드·열람</t>
         </is>
@@ -11264,9 +10894,9 @@
           <t>- [미리보기] 후 [PDF] 다운로드</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
@@ -11274,108 +10904,108 @@
           <t>- 미리보기 팝업 표출 및 PDF 다운로드</t>
         </is>
       </c>
-      <c r="M42" s="67" t="inlineStr">
+      <c r="M42" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="78" customHeight="1" s="48">
-      <c r="A43" s="35" t="n">
+    <row r="43" ht="78" customHeight="1" s="46">
+      <c r="A43" s="43" t="n">
         <v>38</v>
       </c>
-      <c r="B43" s="69" t="n"/>
-      <c r="C43" s="69" t="n"/>
-      <c r="D43" s="69" t="n"/>
-      <c r="E43" s="35" t="inlineStr">
+      <c r="B43" s="45" t="n"/>
+      <c r="C43" s="45" t="n"/>
+      <c r="D43" s="45" t="n"/>
+      <c r="E43" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-06-04</t>
         </is>
       </c>
-      <c r="F43" s="35" t="inlineStr">
+      <c r="F43" s="43" t="inlineStr">
         <is>
           <t>[화면] 보고서 목록</t>
         </is>
       </c>
-      <c r="G43" s="36" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-008-01</t>
         </is>
       </c>
-      <c r="H43" s="35" t="inlineStr">
+      <c r="H43" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-01</t>
         </is>
       </c>
-      <c r="I43" s="37" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>민원 분석 결과 보고서 목록 조회
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J43" s="38" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>- 자동생성 보고서 목록(보고서명/배포주기/생성자/부서/생성일/상태·미리보기·PDF·DOCX)
 - 직접생성 보고서 목록(내보내기 출처/분석기간/생성자/부서·미리보기·다운로드)</t>
         </is>
       </c>
-      <c r="K43" s="39" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L43" s="38" t="inlineStr">
+      <c r="L43" s="1" t="inlineStr">
         <is>
           <t>- 보고서 목록 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M43" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M43" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="78" customHeight="1" s="48">
-      <c r="A44" s="67" t="n">
+    <row r="44" ht="78" customHeight="1" s="46">
+      <c r="A44" s="43" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="67" t="inlineStr">
+      <c r="B44" s="43" t="inlineStr">
         <is>
           <t>ITS-PAR-07</t>
         </is>
       </c>
-      <c r="C44" s="67" t="inlineStr">
+      <c r="C44" s="43" t="inlineStr">
         <is>
           <t>감시 솔루션 데이터 융합(AI 어시스턴트 질의) → 통합분석 → 보고서</t>
         </is>
       </c>
-      <c r="D44" s="67" t="inlineStr">
+      <c r="D44" s="43" t="inlineStr">
         <is>
           <t>서비스관리자,
 일반사용자</t>
         </is>
       </c>
-      <c r="E44" s="67" t="inlineStr">
+      <c r="E44" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-07-01</t>
         </is>
       </c>
-      <c r="F44" s="67" t="inlineStr">
+      <c r="F44" s="43" t="inlineStr">
         <is>
           <t>AI 대화 세션 관리(융합 질의)</t>
         </is>
       </c>
-      <c r="G44" s="22" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-010-01</t>
         </is>
       </c>
-      <c r="H44" s="67" t="inlineStr">
+      <c r="H44" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-005-04</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>데이터 융합 질의·통합분석</t>
         </is>
@@ -11386,7 +11016,7 @@
 - 상관관계·종합 인사이트 도출</t>
         </is>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -11396,92 +11026,92 @@
           <t>- 두 솔루션 데이터가 결합되어 상관관계·종합 인사이트가 시각화</t>
         </is>
       </c>
-      <c r="M44" s="67" t="inlineStr">
+      <c r="M44" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="78" customHeight="1" s="48">
-      <c r="A45" s="35" t="n">
+    <row r="45" ht="78" customHeight="1" s="46">
+      <c r="A45" s="43" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="68" t="n"/>
-      <c r="C45" s="68" t="n"/>
-      <c r="D45" s="68" t="n"/>
-      <c r="E45" s="35" t="inlineStr">
+      <c r="B45" s="44" t="n"/>
+      <c r="C45" s="44" t="n"/>
+      <c r="D45" s="44" t="n"/>
+      <c r="E45" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-07-02</t>
         </is>
       </c>
-      <c r="F45" s="35" t="inlineStr">
+      <c r="F45" s="43" t="inlineStr">
         <is>
           <t>[화면] AI 어시스턴트(통합분석)</t>
         </is>
       </c>
-      <c r="G45" s="36" t="n"/>
-      <c r="H45" s="35" t="inlineStr">
+      <c r="G45" s="13" t="n"/>
+      <c r="H45" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-005-04</t>
         </is>
       </c>
-      <c r="I45" s="37" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>민원데이터와 감시(화재·안전) 데이터를 결합한 통합분석
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J45" s="38" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>- 채팅 영역
 - 결합이 필요한 질문에 AI 에이전트 호출·융합 데이터에서 종합 인사이트 도출
 - 결과를 AI 어시스턴트 답변으로 표시(리포트 생성 버튼 제공)</t>
         </is>
       </c>
-      <c r="K45" s="39" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L45" s="38" t="inlineStr">
+      <c r="L45" s="1" t="inlineStr">
         <is>
           <t>- AI 어시스턴트(통합분석) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M45" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M45" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="78" customHeight="1" s="48">
-      <c r="A46" s="67" t="n">
+    <row r="46" ht="78" customHeight="1" s="46">
+      <c r="A46" s="43" t="n">
         <v>41</v>
       </c>
-      <c r="B46" s="69" t="n"/>
-      <c r="C46" s="69" t="n"/>
-      <c r="D46" s="69" t="n"/>
-      <c r="E46" s="67" t="inlineStr">
+      <c r="B46" s="45" t="n"/>
+      <c r="C46" s="45" t="n"/>
+      <c r="D46" s="45" t="n"/>
+      <c r="E46" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-07-03</t>
         </is>
       </c>
-      <c r="F46" s="67" t="inlineStr">
+      <c r="F46" s="43" t="inlineStr">
         <is>
           <t>보고서 목록 조회(반영)</t>
         </is>
       </c>
-      <c r="G46" s="22" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-008-01</t>
         </is>
       </c>
-      <c r="H46" s="67" t="inlineStr">
+      <c r="H46" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-004-01</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>융합 분석 보고서 반영</t>
         </is>
@@ -11491,7 +11121,7 @@
           <t>- 융합 분석 결과 보고서 내보내기·확인</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -11501,52 +11131,52 @@
           <t>- 융합 분석 인사이트가 보고서에 반영·다운로드</t>
         </is>
       </c>
-      <c r="M46" s="67" t="inlineStr">
+      <c r="M46" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="78" customHeight="1" s="48">
-      <c r="A47" s="67" t="n">
+    <row r="47" ht="78" customHeight="1" s="46">
+      <c r="A47" s="43" t="n">
         <v>42</v>
       </c>
-      <c r="B47" s="67" t="inlineStr">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>ITS-PAR-08</t>
         </is>
       </c>
-      <c r="C47" s="67" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>분석지표 가중치·설정 전환 → 기능 재검증</t>
         </is>
       </c>
-      <c r="D47" s="67" t="inlineStr">
+      <c r="D47" s="43" t="inlineStr">
         <is>
           <t>시스템관리자</t>
         </is>
       </c>
-      <c r="E47" s="67" t="inlineStr">
+      <c r="E47" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-01</t>
         </is>
       </c>
-      <c r="F47" s="67" t="inlineStr">
+      <c r="F47" s="43" t="inlineStr">
         <is>
           <t>분석지표 가중치 조회</t>
         </is>
       </c>
-      <c r="G47" s="22" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-011-01</t>
         </is>
       </c>
-      <c r="H47" s="67" t="inlineStr">
+      <c r="H47" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-03</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>분석모델별 지표·가중치 조회</t>
         </is>
@@ -11556,7 +11186,7 @@
           <t>- 분석지표 가중치 화면 진입, 분석모델별 지표·가중치 목록 확인</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -11566,40 +11196,40 @@
           <t>- 분석모델별 지표·가중치가 정상 조회</t>
         </is>
       </c>
-      <c r="M47" s="67" t="inlineStr">
+      <c r="M47" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="78" customHeight="1" s="48">
-      <c r="A48" s="67" t="n">
+    <row r="48" ht="78" customHeight="1" s="46">
+      <c r="A48" s="43" t="n">
         <v>43</v>
       </c>
-      <c r="B48" s="68" t="n"/>
-      <c r="C48" s="68" t="n"/>
-      <c r="D48" s="68" t="n"/>
-      <c r="E48" s="67" t="inlineStr">
+      <c r="B48" s="44" t="n"/>
+      <c r="C48" s="44" t="n"/>
+      <c r="D48" s="44" t="n"/>
+      <c r="E48" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-02</t>
         </is>
       </c>
-      <c r="F48" s="67" t="inlineStr">
+      <c r="F48" s="43" t="inlineStr">
         <is>
           <t>분석지표 가중치 저장</t>
         </is>
       </c>
-      <c r="G48" s="22" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-011-02</t>
         </is>
       </c>
-      <c r="H48" s="67" t="inlineStr">
+      <c r="H48" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-03</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>타 지자체 기준 가중치 변경·저장(확산)</t>
         </is>
@@ -11609,7 +11239,7 @@
           <t>- 대상 지역 여건에 맞는 지표·가중치로 변경 후 저장</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -11619,40 +11249,40 @@
           <t>- 변경 가중치가 저장되고 변경이력이 함께 기록</t>
         </is>
       </c>
-      <c r="M48" s="67" t="inlineStr">
+      <c r="M48" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="78" customHeight="1" s="48">
-      <c r="A49" s="67" t="n">
+    <row r="49" ht="78" customHeight="1" s="46">
+      <c r="A49" s="43" t="n">
         <v>44</v>
       </c>
-      <c r="B49" s="68" t="n"/>
-      <c r="C49" s="68" t="n"/>
-      <c r="D49" s="68" t="n"/>
-      <c r="E49" s="67" t="inlineStr">
+      <c r="B49" s="44" t="n"/>
+      <c r="C49" s="44" t="n"/>
+      <c r="D49" s="44" t="n"/>
+      <c r="E49" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-03</t>
         </is>
       </c>
-      <c r="F49" s="67" t="inlineStr">
+      <c r="F49" s="43" t="inlineStr">
         <is>
           <t>가중치 변경이력 조회</t>
         </is>
       </c>
-      <c r="G49" s="22" t="inlineStr">
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-011-03</t>
         </is>
       </c>
-      <c r="H49" s="67" t="inlineStr">
+      <c r="H49" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-03</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>변경이력 조회</t>
         </is>
@@ -11662,7 +11292,7 @@
           <t>- 변경항목·내용·사유·변경자 확인</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -11672,40 +11302,40 @@
           <t>- 가중치 변경이력이 항목·사유·변경자와 함께 표출</t>
         </is>
       </c>
-      <c r="M49" s="67" t="inlineStr">
+      <c r="M49" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="78" customHeight="1" s="48">
-      <c r="A50" s="67" t="n">
+    <row r="50" ht="78" customHeight="1" s="46">
+      <c r="A50" s="43" t="n">
         <v>45</v>
       </c>
-      <c r="B50" s="68" t="n"/>
-      <c r="C50" s="68" t="n"/>
-      <c r="D50" s="68" t="n"/>
-      <c r="E50" s="67" t="inlineStr">
+      <c r="B50" s="44" t="n"/>
+      <c r="C50" s="44" t="n"/>
+      <c r="D50" s="44" t="n"/>
+      <c r="E50" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-04</t>
         </is>
       </c>
-      <c r="F50" s="67" t="inlineStr">
+      <c r="F50" s="43" t="inlineStr">
         <is>
           <t>가중치 설정 롤백</t>
         </is>
       </c>
-      <c r="G50" s="22" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-011-04</t>
         </is>
       </c>
-      <c r="H50" s="67" t="inlineStr">
+      <c r="H50" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-03</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>이전 설정 롤백</t>
         </is>
@@ -11715,7 +11345,7 @@
           <t>- 특정 변경이력 선택 후 롤백</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -11725,46 +11355,46 @@
           <t>- 이전 가중치 설정으로 정상 복원</t>
         </is>
       </c>
-      <c r="M50" s="67" t="inlineStr">
+      <c r="M50" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="78" customHeight="1" s="48">
-      <c r="A51" s="35" t="n">
+    <row r="51" ht="78" customHeight="1" s="46">
+      <c r="A51" s="43" t="n">
         <v>46</v>
       </c>
-      <c r="B51" s="68" t="n"/>
-      <c r="C51" s="68" t="n"/>
-      <c r="D51" s="68" t="n"/>
-      <c r="E51" s="35" t="inlineStr">
+      <c r="B51" s="44" t="n"/>
+      <c r="C51" s="44" t="n"/>
+      <c r="D51" s="44" t="n"/>
+      <c r="E51" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-05</t>
         </is>
       </c>
-      <c r="F51" s="35" t="inlineStr">
+      <c r="F51" s="43" t="inlineStr">
         <is>
           <t>[화면] 설정_분석지표 가중치설정</t>
         </is>
       </c>
-      <c r="G51" s="36" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-011-01~04</t>
         </is>
       </c>
-      <c r="H51" s="35" t="inlineStr">
+      <c r="H51" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-03</t>
         </is>
       </c>
-      <c r="I51" s="37" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>분석지표 가중치를 지역 여건에 맞게 조정·이력 관리
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J51" s="38" t="inlineStr">
+      <c r="J51" s="1" t="inlineStr">
         <is>
           <t>- 분석유형별 탭 가중치 조절
 - 가중치 변경 이력 표시
@@ -11772,50 +11402,50 @@
 - 기본값 초기화(롤백)</t>
         </is>
       </c>
-      <c r="K51" s="39" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L51" s="38" t="inlineStr">
+      <c r="L51" s="1" t="inlineStr">
         <is>
           <t>- 설정_분석지표 가중치설정 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M51" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M51" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="78" customHeight="1" s="48">
-      <c r="A52" s="67" t="n">
+    <row r="52" ht="78" customHeight="1" s="46">
+      <c r="A52" s="43" t="n">
         <v>47</v>
       </c>
-      <c r="B52" s="68" t="n"/>
-      <c r="C52" s="68" t="n"/>
-      <c r="D52" s="68" t="n"/>
-      <c r="E52" s="67" t="inlineStr">
+      <c r="B52" s="44" t="n"/>
+      <c r="C52" s="44" t="n"/>
+      <c r="D52" s="44" t="n"/>
+      <c r="E52" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-06</t>
         </is>
       </c>
-      <c r="F52" s="67" t="inlineStr">
+      <c r="F52" s="43" t="inlineStr">
         <is>
           <t>메뉴별 권한 조회</t>
         </is>
       </c>
-      <c r="G52" s="22" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>PR-CMM-003-01</t>
         </is>
       </c>
-      <c r="H52" s="67" t="inlineStr">
+      <c r="H52" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-02</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>권한별 메뉴 권한 조회</t>
         </is>
@@ -11825,7 +11455,7 @@
           <t>- 좌측 기등록 메뉴목록·우측 권한별 체크 상태 확인</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -11835,40 +11465,40 @@
           <t>- 권한별 메뉴 권한 부여 현황이 정상 조회</t>
         </is>
       </c>
-      <c r="M52" s="67" t="inlineStr">
+      <c r="M52" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="78" customHeight="1" s="48">
-      <c r="A53" s="67" t="n">
+    <row r="53" ht="78" customHeight="1" s="46">
+      <c r="A53" s="43" t="n">
         <v>48</v>
       </c>
-      <c r="B53" s="68" t="n"/>
-      <c r="C53" s="68" t="n"/>
-      <c r="D53" s="68" t="n"/>
-      <c r="E53" s="67" t="inlineStr">
+      <c r="B53" s="44" t="n"/>
+      <c r="C53" s="44" t="n"/>
+      <c r="D53" s="44" t="n"/>
+      <c r="E53" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-07</t>
         </is>
       </c>
-      <c r="F53" s="67" t="inlineStr">
+      <c r="F53" s="43" t="inlineStr">
         <is>
           <t>메뉴별 권한 설정</t>
         </is>
       </c>
-      <c r="G53" s="22" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>PR-CMM-003-02</t>
         </is>
       </c>
-      <c r="H53" s="67" t="inlineStr">
+      <c r="H53" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-02</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>권한 부여·회수</t>
         </is>
@@ -11878,7 +11508,7 @@
           <t>- 기등록 메뉴에 권한 체크(INSERT)/해제(DELETE) 후 저장</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -11888,96 +11518,96 @@
           <t>- 체크=부여, 해제=회수가 반영되고 재로그인 시 메뉴 구성에 적용</t>
         </is>
       </c>
-      <c r="M53" s="67" t="inlineStr">
+      <c r="M53" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="78" customHeight="1" s="48">
-      <c r="A54" s="35" t="n">
+    <row r="54" ht="78" customHeight="1" s="46">
+      <c r="A54" s="43" t="n">
         <v>49</v>
       </c>
-      <c r="B54" s="68" t="n"/>
-      <c r="C54" s="68" t="n"/>
-      <c r="D54" s="68" t="n"/>
-      <c r="E54" s="35" t="inlineStr">
+      <c r="B54" s="44" t="n"/>
+      <c r="C54" s="44" t="n"/>
+      <c r="D54" s="44" t="n"/>
+      <c r="E54" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-08</t>
         </is>
       </c>
-      <c r="F54" s="35" t="inlineStr">
+      <c r="F54" s="43" t="inlineStr">
         <is>
           <t>[화면] 설정_메뉴 권한관리</t>
         </is>
       </c>
-      <c r="G54" s="36" t="inlineStr">
+      <c r="G54" s="13" t="inlineStr">
         <is>
           <t>PR-CMM-003-01~02</t>
         </is>
       </c>
-      <c r="H54" s="35" t="inlineStr">
+      <c r="H54" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-02</t>
         </is>
       </c>
-      <c r="I54" s="37" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>메뉴별 사용 권한그룹 지정
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J54" s="38" t="inlineStr">
+      <c r="J54" s="1" t="inlineStr">
         <is>
           <t>- 메뉴별 사용 가능 권한그룹 지정 탭
 - 메뉴 클릭→오른쪽에서 권한그룹 지정(체크 부여/해제)
 - 시스템·서비스관리자 전체권한 고정, 일반사용자 체크 부여·권한 저장</t>
         </is>
       </c>
-      <c r="K54" s="39" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L54" s="38" t="inlineStr">
+      <c r="L54" s="1" t="inlineStr">
         <is>
           <t>- 설정_메뉴 권한관리 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M54" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M54" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="78" customHeight="1" s="48">
-      <c r="A55" s="67" t="n">
+    <row r="55" ht="78" customHeight="1" s="46">
+      <c r="A55" s="43" t="n">
         <v>50</v>
       </c>
-      <c r="B55" s="68" t="n"/>
-      <c r="C55" s="68" t="n"/>
-      <c r="D55" s="68" t="n"/>
-      <c r="E55" s="67" t="inlineStr">
+      <c r="B55" s="44" t="n"/>
+      <c r="C55" s="44" t="n"/>
+      <c r="D55" s="44" t="n"/>
+      <c r="E55" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-09</t>
         </is>
       </c>
-      <c r="F55" s="67" t="inlineStr">
+      <c r="F55" s="43" t="inlineStr">
         <is>
           <t>메뉴 권한 관리 조회</t>
         </is>
       </c>
-      <c r="G55" s="22" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t>미정의(메뉴 권한 관리)</t>
         </is>
       </c>
-      <c r="H55" s="67" t="inlineStr">
+      <c r="H55" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-01</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>사용자 계정·권한그룹 현황 조회</t>
         </is>
@@ -11989,7 +11619,7 @@
 - 메뉴 단위 저장</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -11999,42 +11629,42 @@
           <t>- 사용자 계정 현황이 권한그룹별로 조회되고 검색·필터 정상 동작</t>
         </is>
       </c>
-      <c r="M55" s="67" t="inlineStr">
+      <c r="M55" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="78" customHeight="1" s="48">
-      <c r="A56" s="35" t="n">
+    <row r="56" ht="78" customHeight="1" s="46">
+      <c r="A56" s="43" t="n">
         <v>51</v>
       </c>
-      <c r="B56" s="68" t="n"/>
-      <c r="C56" s="68" t="n"/>
-      <c r="D56" s="68" t="n"/>
-      <c r="E56" s="35" t="inlineStr">
+      <c r="B56" s="44" t="n"/>
+      <c r="C56" s="44" t="n"/>
+      <c r="D56" s="44" t="n"/>
+      <c r="E56" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-10</t>
         </is>
       </c>
-      <c r="F56" s="35" t="inlineStr">
+      <c r="F56" s="43" t="inlineStr">
         <is>
           <t>[화면] 설정_메뉴 권한 관리</t>
         </is>
       </c>
-      <c r="G56" s="36" t="n"/>
-      <c r="H56" s="35" t="inlineStr">
+      <c r="G56" s="13" t="n"/>
+      <c r="H56" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-006-01</t>
         </is>
       </c>
-      <c r="I56" s="37" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>사용자 계정 현황 조회·권한그룹별 관리
 (화면설계 점검)</t>
         </is>
       </c>
-      <c r="J56" s="38" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr">
         <is>
           <t>- 메뉴 권한 관리/분석 지표 가중치 설정 2개 탭
 - 메뉴별 권한 그룹 지정(시스템 관리자 항상 허용, 일반 사용자 관리 메뉴 부여 불가)
@@ -12042,50 +11672,50 @@
 - 메뉴 단위 저장</t>
         </is>
       </c>
-      <c r="K56" s="39" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L56" s="38" t="inlineStr">
+      <c r="L56" s="1" t="inlineStr">
         <is>
           <t>- 설정_메뉴 권한 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
-      <c r="M56" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="M56" s="43" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="78" customHeight="1" s="48">
-      <c r="A57" s="67" t="n">
+    <row r="57" ht="78" customHeight="1" s="46">
+      <c r="A57" s="43" t="n">
         <v>52</v>
       </c>
-      <c r="B57" s="69" t="n"/>
-      <c r="C57" s="69" t="n"/>
-      <c r="D57" s="69" t="n"/>
-      <c r="E57" s="67" t="inlineStr">
+      <c r="B57" s="45" t="n"/>
+      <c r="C57" s="45" t="n"/>
+      <c r="D57" s="45" t="n"/>
+      <c r="E57" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-08-11</t>
         </is>
       </c>
-      <c r="F57" s="67" t="inlineStr">
+      <c r="F57" s="43" t="inlineStr">
         <is>
           <t>설정 전환 후 기능 재검증</t>
         </is>
       </c>
-      <c r="G57" s="22" t="inlineStr">
+      <c r="G57" s="13" t="inlineStr">
         <is>
           <t>PR-PAR-003-01 외 주요 분석</t>
         </is>
       </c>
-      <c r="H57" s="67" t="inlineStr">
+      <c r="H57" s="43" t="inlineStr">
         <is>
           <t>UI-PAR-003</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>설정 전환 후 주요 분석 재실행</t>
         </is>
@@ -12095,7 +11725,7 @@
           <t>- 변경된 지역·가중치·권한 기준으로 집중구역/시뮬레이션/투자우선순위 재실행</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
@@ -12105,54 +11735,54 @@
           <t>- 변경 설정 기준으로 주요 분석 기능이 오류 없이 정상 동작</t>
         </is>
       </c>
-      <c r="M57" s="67" t="inlineStr">
+      <c r="M57" s="43" t="inlineStr">
         <is>
           <t>정정</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="78" customHeight="1" s="48">
-      <c r="A58" s="67" t="n">
+    <row r="58" ht="78" customHeight="1" s="46">
+      <c r="A58" s="43" t="n">
         <v>53</v>
       </c>
-      <c r="B58" s="67" t="inlineStr">
+      <c r="B58" s="43" t="inlineStr">
         <is>
           <t>ITS-PAR-09</t>
         </is>
       </c>
-      <c r="C58" s="67" t="inlineStr">
+      <c r="C58" s="43" t="inlineStr">
         <is>
           <t>예외·비정상 흐름 검증(권한)</t>
         </is>
       </c>
-      <c r="D58" s="67" t="inlineStr">
+      <c r="D58" s="43" t="inlineStr">
         <is>
           <t>시스템관리자,
 서비스관리자,
 일반사용자</t>
         </is>
       </c>
-      <c r="E58" s="67" t="inlineStr">
+      <c r="E58" s="43" t="inlineStr">
         <is>
           <t>TT-PAR-09-01</t>
         </is>
       </c>
-      <c r="F58" s="67" t="inlineStr">
+      <c r="F58" s="43" t="inlineStr">
         <is>
           <t>권한 범위 초과 접근 차단</t>
         </is>
       </c>
-      <c r="G58" s="22" t="inlineStr">
+      <c r="G58" s="13" t="inlineStr">
         <is>
           <t>PR-CMM-003-03</t>
         </is>
       </c>
-      <c r="H58" s="67" t="inlineStr">
+      <c r="H58" s="43" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>비인가 접근 차단</t>
         </is>
@@ -12162,7 +11792,7 @@
           <t>- 비인가·타 부서 권한 계정으로 관리 기능/데이터 접근 시도</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="K58" s="3" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
@@ -12172,15 +11802,15 @@
           <t>- 권한 범위 초과 접근이 차단되고 안내 메시지 표출</t>
         </is>
       </c>
-      <c r="M58" s="67" t="inlineStr">
+      <c r="M58" s="43" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="78" customHeight="1" s="48"/>
-    <row r="60" ht="78" customHeight="1" s="48"/>
-    <row r="61" ht="78" customHeight="1" s="48"/>
+    <row r="59" ht="78" customHeight="1" s="46"/>
+    <row r="60" ht="78" customHeight="1" s="46"/>
+    <row r="61" ht="78" customHeight="1" s="46"/>
   </sheetData>
   <mergeCells count="38">
     <mergeCell ref="C4:C5"/>
@@ -12191,11 +11821,11 @@
     <mergeCell ref="D30:D32"/>
     <mergeCell ref="D25:D29"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D47:D57"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="D44:D46"/>
+    <mergeCell ref="B33:B39"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="B33:B39"/>
+    <mergeCell ref="D47:D57"/>
     <mergeCell ref="D33:D39"/>
     <mergeCell ref="B6:B16"/>
     <mergeCell ref="C40:C43"/>
@@ -12233,202 +11863,202 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="17.1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="6" customWidth="1" style="48" min="1" max="1"/>
-    <col width="12" customWidth="1" style="48" min="2" max="2"/>
-    <col width="70" customWidth="1" style="48" min="3" max="3"/>
-    <col width="20" customWidth="1" style="48" min="4" max="4"/>
-    <col width="45" customWidth="1" style="48" min="5" max="5"/>
-    <col width="10" customWidth="1" style="48" min="6" max="6"/>
-    <col width="12" customWidth="1" style="48" min="7" max="7"/>
+    <col width="6" customWidth="1" style="46" min="1" max="1"/>
+    <col width="12" customWidth="1" style="46" min="2" max="2"/>
+    <col width="70" customWidth="1" style="46" min="3" max="3"/>
+    <col width="20" customWidth="1" style="46" min="4" max="4"/>
+    <col width="45" customWidth="1" style="46" min="5" max="5"/>
+    <col width="10" customWidth="1" style="46" min="6" max="6"/>
+    <col width="12" customWidth="1" style="46" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1" s="48">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="46">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>통합테스트 이슈사항</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>이슈 내용</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>관련 통합테스트 ID</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>조치 방안</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="G3" s="28" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>등록일</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" s="48">
-      <c r="A4" s="29" t="n">
+    <row r="4" ht="60" customHeight="1" s="46">
+      <c r="A4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>범위 미확정</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>실시간 공영주차장 감시 대응 솔루션의 산출물 범위 및 연동 인터페이스가 미확정 상태로, 융합 통합분석 시나리오를 잠정 작성함. 결합 키·연계 방식(API/배치) 확정 후 시나리오 재검토 필요</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>TT-PAR-A01-14</t>
         </is>
       </c>
-      <c r="E4" s="40" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>감시 대응 솔루션 담당과 인터페이스 정의서 협의 후 시나리오 확정</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>진행중</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" s="48">
-      <c r="A5" s="29" t="n">
+    <row r="5" ht="60" customHeight="1" s="46">
+      <c r="A5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>설계 미반영</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>단위테스트(M04)의 설정 화면(UT-SET-01~06)에 대응하는 화면이 화면설계서에 없어 화면 ID를 공란 처리함</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="40" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>화면설계서에 설정 화면 추가 또는 테스트 항목 조정</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>검토중</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" s="48">
-      <c r="A6" s="29" t="n">
+    <row r="6" ht="60" customHeight="1" s="46">
+      <c r="A6" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>테스트 환경</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>테스트데이터를 권한 유형으로만 기재함. 실증 환경에서 권한별 계정 발급 후 테스트 수행 필요</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="E6" s="40" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>실증 착수 시 권한별 계정 발급 후 테스트 수행</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" s="48">
-      <c r="A7" s="29" t="n">
+    <row r="7" ht="60" customHeight="1" s="46">
+      <c r="A7" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>미수행</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>통합테스트 미수행 상태로 결과서의 1차·2차 상태·점검자·점검일이 공란임</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="E7" s="40" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>통합테스트 수행 후 결과 기입</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="48"/>
+    <row r="8" ht="60" customHeight="1" s="46"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Audit/JJ_PD_IP_D27_통합테스트계획서_v1.0_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_D27_통합테스트계획서_v1.0_이노팸.xlsx
@@ -8313,7 +8313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="17"/>
   <cols>
     <col width="8.1640625" customWidth="1" style="27" min="1" max="1"/>
@@ -8328,6 +8328,7 @@
     <col width="11.33203125" customWidth="1" style="27" min="15" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="27.5" customHeight="1" s="46">
       <c r="E2" s="6" t="n"/>
       <c r="F2" s="29" t="inlineStr">
@@ -8358,6 +8359,11 @@
       </c>
       <c r="I3" s="38" t="n"/>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="26.25" customHeight="1" s="46">
       <c r="A9" s="36" t="inlineStr">
         <is>
@@ -8412,6 +8418,19 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="43.5" customHeight="1" s="46">
       <c r="B28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
@@ -8460,7 +8479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="17"/>
   <cols>
     <col width="15.1640625" customWidth="1" style="40" min="1" max="1"/>
@@ -8471,6 +8490,7 @@
     <col width="11.33203125" customWidth="1" style="40" min="11" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26.25" customHeight="1" s="46">
       <c r="A2" s="39" t="inlineStr">
         <is>
@@ -8478,6 +8498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24.75" customHeight="1" s="46">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -8910,7 +8931,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
@@ -11018,7 +11039,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
@@ -11070,7 +11091,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L45" s="1" t="inlineStr">
@@ -11123,7 +11144,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L46" s="1" t="inlineStr">
@@ -11153,7 +11174,7 @@
       </c>
       <c r="D47" s="43" t="inlineStr">
         <is>
-          <t>시스템관리자</t>
+          <t>서비스관리자</t>
         </is>
       </c>
       <c r="E47" s="43" t="inlineStr">
@@ -11188,7 +11209,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
@@ -11241,7 +11262,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L48" s="1" t="inlineStr">
@@ -11294,7 +11315,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L49" s="1" t="inlineStr">
@@ -11347,7 +11368,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L50" s="1" t="inlineStr">
@@ -11404,7 +11425,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L51" s="1" t="inlineStr">
@@ -11457,7 +11478,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L52" s="1" t="inlineStr">
@@ -11510,7 +11531,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L53" s="1" t="inlineStr">
@@ -11566,7 +11587,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L54" s="1" t="inlineStr">
@@ -11621,7 +11642,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L55" s="1" t="inlineStr">
@@ -11674,7 +11695,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L56" s="1" t="inlineStr">
@@ -11727,7 +11748,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>서비스관리자 권한 계정</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
@@ -11757,8 +11778,7 @@
       </c>
       <c r="D58" s="43" t="inlineStr">
         <is>
-          <t>시스템관리자,
-서비스관리자,
+          <t>서비스관리자,
 일반사용자</t>
         </is>
       </c>
@@ -11881,6 +11901,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
